--- a/generator/output/master/suppliers.xlsx
+++ b/generator/output/master/suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>PostalAddress</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -463,6 +463,16 @@
         </is>
       </c>
       <c r="J1" t="inlineStr">
+        <is>
+          <t>LeadTimeDays</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SupplierRating</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>IsActive</t>
         </is>
@@ -471,51 +481,6720 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'SUP015'}</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bio Foods Ltd</t>
+          <t>Brookside Dairy Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yoghurt</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allison Hill</t>
+          <t>Grace Achieng</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321.581.9600</t>
+          <t>+254714246316</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>williamjohnson@baldwin.net</t>
+          <t>admin@brooksidedairyltd.co.ke</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Robinsonshire</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>65423 Garcia Light
-West Melanieview, AS 06196</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SUP002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sameer Agriculture</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>James Odhiambo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+254713343962</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>support@sameeragriculture.ac.ke</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mombasa CBD</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SUP003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>New KCC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Faith Muthoni</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+254757391704</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>info@newkcc.co.ke</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUP004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kinangop Dairy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Peter Kariuki</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+254706476417</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>orders@kinangopdairy.ac.ke</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Murang'a</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Murang'a Town</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Net 30</t>
         </is>
       </c>
-      <c r="J2" t="b">
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUP005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Githunguri Dairy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Peter Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+254718969693</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>admin@githunguridairy.ac.ke</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ngong</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUP006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Happy Cow Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mercy Odhiambo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+254799344098</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>info@happycowltd.ke</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kiambu</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ruiru</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUP007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Delamere Dairy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Brian Mutua</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+254769816751</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>admin@delameredairy.co.ke</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kirinyaga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kerugoya</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUP008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lato Milk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Esther Mutua</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+254760821590</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>support@latomilk.co.ke</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Uasin Gishu</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eldoret</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUP009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Upfield Kenya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Joyce Kariuki</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+254717169403</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sales@upfieldkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kakamega</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kakamega Town</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUP010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Unga Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Grace Njoroge</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+254715881177</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>support@ungagroup.ac.ke</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUP011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capwell Industries</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Faith Njoroge</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+254742617488</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>info@capwellindustries.co.ke</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Embu</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Embu Town</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUP012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pembe Flour Mills</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Esther Kariuki</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+254758590785</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>support@pembeflourmills.ke</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mombasa CBD</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SUP013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>West Kenya Sugar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Joyce Wanjiku</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+254718555884</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sales@westkenyasugar.ke</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SUP014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mumias Sugar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kevin Kiprotich</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+254706755674</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>orders@mumiassugar.ac.ke</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SUP015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Raha Premium</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Paul Omondi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+254741120422</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>info@rahapremium.ke</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Uasin Gishu</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Eldoret</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SUP016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bidco Africa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Peter Wambui</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+254797172574</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>support@bidcoafrica.co.ke</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SUP017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kapa Oil Refineries</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Paul Kimani</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+254713665492</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>admin@kapaoilrefineries.ac.ke</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Makutano</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>13</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SUP018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rina Industries</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Samuel Muthoni</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+254707359947</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>sales@rinaindustries.co.ke</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kirinyaga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kerugoya</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SUP019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kasuku Foods</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Peter Otieno</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+254714170674</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>info@kasukufoods.ke</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kakamega</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kakamega Town</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SUP020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Exe Consumer Brands</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Victor Ouma</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+254740354801</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>accounts@execonsumerbrands.ke</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SUP021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Crown Foods</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dorcas Otieno</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>+254768785197</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>admin@crownfoods.co.ke</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Nyali</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SUP022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Top Fry Ltd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Brian Chebet</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>+254745570405</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>sales@topfryltd.ke</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kitengela</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SUP023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rift Valley Products</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dennis Wanjiku</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>+254703783823</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>support@riftvalleyproducts.co.ke</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Athi River</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>14</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SUP024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ken Salt Ltd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Brian Kariuki</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>+254703272634</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>accounts@kensaltltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kwale</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Diani</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SUP025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Coca-Cola Beverages Kenya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Dennis Wambui</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+254709299122</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>orders@coca-colabeverageskenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nyeri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Nyeri Town</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>11</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SUP026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Varun Beverages Kenya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>John Ouma</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+254740627276</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>support@varunbeverageskenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Murang'a</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Murang'a Town</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SUP027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Red Bull Kenya</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Faith Kariuki</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+254707697347</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>sales@redbullkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Trans Nzoia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SUP028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Monster Energy Kenya</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Grace Chebet</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>+254762850981</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>orders@monsterenergykenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SUP029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Del Monte Kenya</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Juices</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Peter Mwangi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+254729751332</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>support@delmontekenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SUP030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kevian Kenya</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Juices</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Faith Maina</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>+254718265409</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>accounts@keviankenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Kirinyaga</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kerugoya</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SUP031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Keringet Mineral Water</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>James Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+254719795613</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>info@keringetmineralwater.co.ke</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SUP032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aquamist Ltd</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mercy Nyambura</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>+254713852470</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>orders@aquamistltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Naivasha</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SUP033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Highlands Drinks Ltd</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Peter Kimani</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>+254798390120</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>info@highlandsdrinksltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Meru Town</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>14</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SUP034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ketepa Ltd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dennis Kimani</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>+254746110139</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>info@ketepaltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Uasin Gishu</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Eldoret</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SUP035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gold Crown Foods</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ann Njoroge</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>+254702423232</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>orders@goldcrownfoods.co.ke</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SUP036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nestlé Kenya</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Paul Njoroge</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>+254715270395</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>sales@nestlékenya.ke</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Kirinyaga</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kerugoya</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SUP037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dormans Coffee</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Grace Kiptoo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>+254795835343</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>info@dormanscoffee.ke</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Mombasa CBD</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SUP038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Java House Coffee</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mercy Achieng</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>+254714124813</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>admin@javahousecoffee.co.ke</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SUP039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mini Bakeries</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Samuel Kariuki</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>+254768984642</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>support@minibakeries.ke</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Maua</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SUP040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Broadways Bakery</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>John Wanjiku</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>+254758555673</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>orders@broadwaysbakery.ac.ke</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SUP041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Farmer's Choice</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Meat &amp; Poultry</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Victor Chebet</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>+254716146542</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>admin@farmer'schoice.ke</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ngong</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>10</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SUP042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kenchic Ltd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Meat &amp; Poultry</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ann Odhiambo</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>+254762446239</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>support@kenchicltd.ke</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SUP043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brade Gate Poultry</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Meat &amp; Poultry</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Joyce Kariuki</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>+254769410016</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>support@bradegatepoultry.co.ke</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nyeri</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Nyeri Town</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SUP044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Victory Farms</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fish &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Esther Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>+254798100425</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>orders@victoryfarms.ke</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Uasin Gishu</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Eldoret</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SUP045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sea Harvest Kenya</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fish &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Dorcas Muthoni</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>+254768324082</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>support@seaharvestkenya.ke</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Murang'a</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Murang'a Town</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>14</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SUP046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Big Cold Ltd</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frozen Foods</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Peter Achieng</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>+254768425498</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>sales@bigcoldltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nyeri</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Nyeri Town</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SUP047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tropical Heat Ltd</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Dorcas Kimani</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>+254760703634</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>sales@tropicalheatltd.ac.ke</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Trans Nzoia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SUP048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Propack Kenya</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>David Kimani</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>+254714284430</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>admin@propackkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ruaka</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SUP049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kenafric Industries</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Daniel Muthoni</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+254762656932</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>support@kenafricindustries.ac.ke</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ngong</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>14</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SUP050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Perfetti Van Melle</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ann Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>+254728266889</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>admin@perfettivanmelle.ke</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SUP051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Wrigley East Africa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lucy Achieng</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>+254717561239</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>info@wrigleyeastafrica.ac.ke</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Makutano</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SUP052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cadbury Kenya</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Daniel Njoroge</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>+254714501641</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>admin@cadburykenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SUP053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reckitt Benckiser</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ann Otieno</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+254713973349</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>accounts@reckittbenckiser.ke</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>11</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SUP054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PZ Cussons</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lucy Mwangi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>+254722413118</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>accounts@pzcussons.ke</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>13</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SUP055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Faith Mutua</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>+254727609232</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>info@colgatepalmolive.ke</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Kakamega</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kakamega Town</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>12</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SUP056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GlaxoSmithKline Kenya</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Health &amp; Pharmacy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Daniel Nyambura</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>+254745128276</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>accounts@glaxosmithklinekenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Uasin Gishu</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Eldoret</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>12</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SUP057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble Kenya</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Kevin Otieno</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>+254716497519</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>orders@proctergamblekenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Naivasha</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SUP058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson Kenya</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Baby Care</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Grace Odhiambo</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+254740120324</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>admin@johnsonjohnsonkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Maua</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SUP059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nivea Kenya</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Faith Chebet</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>+254798121369</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>support@niveakenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Kiambu</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Thika</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SUP060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unilever Kenya</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Grace Maina</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>+254710735324</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>support@unileverkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SUP061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pwani Oil Products</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Laundry</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Victor Mwangi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+254719703766</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>admin@pwanioilproducts.ke</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nyeri</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Nyeri Town</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>13</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SUP062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pyrex Kenya</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Kitchenware</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mercy Nyambura</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+254796226935</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>support@pyrexkenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Kakamega</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kakamega Town</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>10</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SUP063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tefal Kenya</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kitchenware</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Joyce Mwangi</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+254799540463</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>accounts@tefalkenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SUP064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Prestige Kenya</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kitchenware</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kevin Kiprotich</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>+254761383201</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>support@prestigekenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Naivasha</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>9</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SUP065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Luminarc Kenya</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kitchenware</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Joyce Achieng</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>+254798190872</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>orders@luminarckenya.ke</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>14</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SUP066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Royalford Kenya</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Kitchenware</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>James Wambui</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>+254799440802</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>sales@royalfordkenya.ke</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Embu</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Embu Town</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SUP067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Samsung Electronics Kenya</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dennis Mwangi</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>+254743300337</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>info@samsungelectronicskenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Trans Nzoia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SUP068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LG Electronics Kenya</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Dorcas Mwangi</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>+254705408528</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>sales@lgelectronicskenya.ke</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Kwale</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Diani</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SUP069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sony Kenya</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ann Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>+254721468900</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>admin@sonykenya.ke</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Kwale</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Diani</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SUP070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Philips Kenya</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>David Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>+254793823688</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>sales@philipskenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>13</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SUP071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ramtons Ltd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paul Kamau</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>+254706973074</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>sales@ramtonsltd.ke</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SUP072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Von Hotpoint</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Grace Otieno</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>+254703680238</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>orders@vonhotpoint.ac.ke</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>12</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SUP073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BIC Kenya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mercy Wambui</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>+254740561865</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>orders@bickenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SUP074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Casio Kenya</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lucy Odhiambo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>+254748760021</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>admin@casiokenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Athi River</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SUP075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Office Point Kenya</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>David Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>+254793536390</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>support@officepointkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Machakos Town</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>11</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SUP076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Text Book Centre</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mercy Ouma</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>+254727420214</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>support@textbookcentre.ac.ke</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SUP077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pedigree Kenya</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Grace Odhiambo</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>+254710351516</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>sales@pedigreekenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SUP078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Whiskas Kenya</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mercy Otieno</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>+254714402099</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>admin@whiskaskenya.ke</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Trans Nzoia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SUP079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Purina Kenya</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Victor Chebet</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>+254727220351</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>support@purinakenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Makutano</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SUP080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SmartHeart Kenya</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Kevin Kamau</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>+254758885339</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>support@smartheartkenya.ke</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Machakos Town</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SUP081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fresh Harvest Suppliers</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fresh Produce</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Samuel Cheruiyot</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>+254741559023</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>info@freshharvestsuppliers.ac.ke</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Embu</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Embu Town</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SUP082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Green Farm Kenya</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fresh Produce</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Faith Ouma</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>+254757121753</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>admin@greenfarmkenya.ke</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Nairobi CBD</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SUP083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nature Fresh Ltd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fresh Produce</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Dorcas Mutua</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>+254711713762</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>accounts@naturefreshltd.ac.ke</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>9</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SUP084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Farm Choice Kenya</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fresh Produce</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Joyce Wanjiku</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>+254799268637</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>orders@farmchoicekenya.ke</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Nyali</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>9</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SUP085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Organic Select Kenya</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fresh Produces</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Dorcas Odhiambo</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>+254720364659</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>orders@organicselectkenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SUP086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Brookside Dairy Ltd - Kakamega Branch</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ann Otieno</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>+254712643623</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>orders@brooksidedairyltd.ac.ke</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>9</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SUP087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Red Bull Kenya - Eldoret Branch</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mercy Muthoni</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>+254769608257</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>info@redbullkenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>11</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SUP088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Broadways Bakery - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ann Odhiambo</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>+254714982277</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>info@broadwaysbakery.ke</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>12</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SUP089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Java House Coffee - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lucy Wambui</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>+254715578975</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>support@javahousecoffee.co.ke</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Maua</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SUP090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Rina Industries - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Joyce Kiprotich</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>+254717960408</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>info@rinaindustries.ke</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Maua</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SUP091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Organic Select Kenya - Thika Branch</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fresh Produces</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Dennis Wambui</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>+254722448588</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>support@organicselectkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Naivasha</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>9</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SUP092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Keringet Mineral Water - Machakos Branch</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Ann Otieno</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>+254720880879</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>accounts@keringetmineralwater.ac.ke</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Embu</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Embu Town</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SUP093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Farm Choice Kenya - Kisumu Branch</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fresh Produce</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Daniel Kiprotich</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>+254757448121</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>info@farmchoicekenya.ke</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Kwale</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Diani</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>10</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SUP094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kasuku Foods - Nyeri Branch</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lucy Mutua</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>+254721753534</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>admin@kasukufoods.ke</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Nakuru Town</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SUP095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sony Kenya - Nyeri Branch</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Dennis Otieno</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>+254759171744</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>sales@sonykenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Murang'a</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Murang'a Town</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>6</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SUP096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GlaxoSmithKline Kenya - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Health &amp; Pharmacy</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Kevin Kamau</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>+254701148225</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>orders@glaxosmithklinekenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ngong</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>7</v>
+      </c>
+      <c r="K97" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SUP097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LG Electronics Kenya - Nyeri Branch</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Kevin Kiptoo</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>+254705739098</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>accounts@lgelectronicskenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SUP098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kevian Kenya - Thika Branch</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Juices</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Grace Mwangi</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>+254796587853</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>orders@keviankenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Maua</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SUP099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Text Book Centre - Eldoret Branch</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Dorcas Kamau</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>+254712503380</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>accounts@textbookcentre.co.ke</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Nyali</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SUP100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Java House Coffee - Nairobi Branch</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>James Ouma</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>+254768916118</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>admin@javahousecoffee.co.ke</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Embu</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Embu Town</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>13</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SUP101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Dormans Coffee - Nakuru Branch</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Faith Chebet</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>+254759362801</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>admin@dormanscoffee.ac.ke</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Trans Nzoia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>12</v>
+      </c>
+      <c r="K102" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SUP102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>West Kenya Sugar - Kakamega Branch</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Dorcas Otieno</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>+254757482584</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>admin@westkenyasugar.co.ke</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Kiambu</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kiambu Town</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>6</v>
+      </c>
+      <c r="K103" t="n">
+        <v>4</v>
+      </c>
+      <c r="L103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SUP103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Varun Beverages Kenya - Kisumu Branch</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Samuel Kiprotich</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>+254717970813</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>sales@varunbeverageskenya.ke</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>9</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SUP104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Victory Farms - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fish &amp; Seafood</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Daniel Achieng</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>+254768859396</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>admin@victoryfarms.ke</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>14</v>
+      </c>
+      <c r="K105" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SUP105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Wrigley East Africa - Nairobi Branch</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>David Muthoni</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>+254723805511</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>admin@wrigleyeastafrica.ac.ke</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Meru</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Makutano</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>11</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SUP106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Propack Kenya - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>James Nyambura</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>+254746443939</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>support@propackkenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Kakamega</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kakamega Town</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SUP107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Mini Bakeries - Kakamega Branch</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Daniel Otieno</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>+254702419149</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>accounts@minibakeries.co.ke</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Mombasa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Mombasa CBD</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SUP108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nivea Kenya - Meru Branch</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Victor Njoroge</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>+254726786735</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>info@niveakenya.ke</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Laikipia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Nanyuki</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>8</v>
+      </c>
+      <c r="K109" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SUP109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Propack Kenya - Nakuru Branch</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Faith Maina</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>+254706818987</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>orders@propackkenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>7</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SUP110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Bidco Africa - Thika Branch</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Brian Nyambura</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>+254701153035</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>orders@bidcoafrica.co.ke</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Mlolongo</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>14</v>
+      </c>
+      <c r="K111" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SUP111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ramtons Ltd - Nakuru Branch</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Faith Omondi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>+254794254721</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>support@ramtonsltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bungoma</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bungoma Town</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" t="n">
+        <v>5</v>
+      </c>
+      <c r="L112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SUP112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Rift Valley Products - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>James Maina</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>+254795926730</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>sales@riftvalleyproducts.ac.ke</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Westlands</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SUP113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PZ Cussons - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lucy Muthoni</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>+254794479625</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>support@pzcussons.ac.ke</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Kajiado</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kitengela</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>9</v>
+      </c>
+      <c r="K114" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SUP114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Happy Cow Ltd - Kisii Branch</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Mercy Muthoni</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>+254761132663</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>info@happycowltd.ke</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Nyandarua</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>8</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SUP115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble Kenya - Mombasa Branch</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Paul Njoroge</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>+254704232321</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>orders@proctergamblekenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Machakos</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Athi River</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>11</v>
+      </c>
+      <c r="K116" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SUP116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pedigree Kenya - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Pet Care</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Samuel Nyambura</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>+254727203996</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>admin@pedigreekenya.co.ke</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Nyeri</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Nyeri Town</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>12</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SUP117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Monster Energy Kenya - Nyeri Branch</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Ann Omondi</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>+254797575528</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>accounts@monsterenergykenya.ke</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kilifi Town</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>3</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SUP118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Highlands Drinks Ltd - Meru Branch</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lucy Odhiambo</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>+254705972176</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>info@highlandsdrinksltd.co.ke</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Nakuru</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Gilgil</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>3</v>
+      </c>
+      <c r="K119" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SUP119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kapa Oil Refineries - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>David Kimani</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>+254722797660</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>accounts@kapaoilrefineries.ac.ke</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Kiambu</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kiambu Town</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>6</v>
+      </c>
+      <c r="K120" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SUP120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Casio Kenya - Kitale Branch</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lucy Achieng</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>+254799213475</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>orders@casiokenya.ac.ke</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Kisumu</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kisumu City</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>3</v>
+      </c>
+      <c r="K121" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L121" t="b">
         <v>1</v>
       </c>
     </row>

--- a/generator/output/master/suppliers.xlsx
+++ b/generator/output/master/suppliers.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>LAIKIPIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,11 +1003,7 @@
           <t>Grace Njoroge</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>+254715881177</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>support@ungagroup.ac.ke</t>
@@ -1183,7 +1179,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>laikipia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3360,11 +3356,7 @@
           <t>+254714501641</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>admin@cadburykenya.co.ke</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Laikipia</t>
@@ -3479,7 +3471,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>bungoma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3510,7 +3502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Colgate Palmolive</t>
+          <t xml:space="preserve"> Colgate Palmolive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3678,7 +3670,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Kenya</t>
+          <t xml:space="preserve"> Johnson &amp; Johnson Kenya</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3691,11 +3683,7 @@
           <t>Grace Odhiambo</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>+254740120324</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>admin@johnsonjohnsonkenya.ac.ke</t>
@@ -4645,7 +4633,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>+254793536390</t>
+          <t>+254718265409</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4928,11 +4916,7 @@
           <t>+254758885339</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>support@smartheartkenya.ke</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>Machakos</t>
@@ -6045,7 +6029,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>+254768916118</t>
+          <t>+254748760021</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6559,7 +6543,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>kilifi</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">

--- a/generator/output/master/suppliers.xlsx
+++ b/generator/output/master/suppliers.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,15 +468,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>LeadTimeDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>SupplierRating</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>IsActive</t>
         </is>
@@ -524,13 +533,16 @@
           <t>Cash on Delivery</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L2" t="b">
+      <c r="J2" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -552,41 +564,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>James Odhiambo</t>
+          <t>Samuel Nyambura</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+254713343962</t>
+          <t>+254701688508</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>support@sameeragriculture.ac.ke</t>
+          <t>sales@sameeragriculture.ac.ke</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mombasa CBD</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L3" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -608,41 +623,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faith Muthoni</t>
+          <t>Kevin Kimani</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+254757391704</t>
+          <t>+254721391369</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>info@newkcc.co.ke</t>
+          <t>sales@newkcc.co.ke</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LAIKIPIA</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Ruaka</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -664,41 +682,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Peter Kariuki</t>
+          <t>Paul Mutua</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+254706476417</t>
+          <t>+254796145561</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>orders@kinangopdairy.ac.ke</t>
+          <t>admin@kinangopdairy.ke</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Kirinyaga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kerugoya</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L5" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -720,41 +741,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Peter Cheruiyot</t>
+          <t>Victor Chebet</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+254718969693</t>
+          <t>+254790172933</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>admin@githunguridairy.ac.ke</t>
+          <t>info@githunguridairy.ac.ke</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L6" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -776,41 +800,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mercy Odhiambo</t>
+          <t>Dorcas Maina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+254799344098</t>
+          <t>254710488162</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>info@happycowltd.ke</t>
+          <t>orders@happycowltd.co.ke</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ruiru</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -832,27 +859,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Brian Mutua</t>
+          <t>Kevin Muthoni</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+254769816751</t>
+          <t>+254724383060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>admin@delameredairy.co.ke</t>
+          <t>admin@delameredairy.ac.ke</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -860,13 +887,16 @@
           <t>Net 60</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L8" t="b">
+      <c r="J8" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -888,27 +918,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Esther Mutua</t>
+          <t>Joyce Kariuki</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+254760821590</t>
+          <t>+254717169403</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>support@latomilk.co.ke</t>
+          <t>sales@latomilk.ac.ke</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -916,13 +946,16 @@
           <t>Cash on Delivery</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L9" t="b">
+      <c r="J9" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -944,41 +977,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Joyce Kariuki</t>
+          <t>Grace Njoroge</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+254717169403</t>
+          <t>+254715881177</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>sales@upfieldkenya.ac.ke</t>
+          <t>support@upfieldkenya.ac.ke</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L10" t="b">
+      <c r="M10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1000,37 +1036,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Grace Njoroge</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Lucy Odhiambo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+254793149405</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>support@ungagroup.ac.ke</t>
+          <t>info@ungagroup.co.ke</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L11" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1052,17 +1095,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faith Njoroge</t>
+          <t>Samuel Mutua</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+254742617488</t>
+          <t>+254746112038</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>info@capwellindustries.co.ke</t>
+          <t>admin@capwellindustries.ac.ke</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1077,16 +1120,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L12" t="b">
+      <c r="M12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1108,41 +1154,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Esther Kariuki</t>
+          <t>James Mutua</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+254758590785</t>
+          <t>+254742898975</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>support@pembeflourmills.ke</t>
+          <t>sales@pembeflourmills.ac.ke</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mombasa CBD</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L13" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1164,41 +1213,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Joyce Wanjiku</t>
+          <t>Paul Omondi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+254718555884</t>
+          <t>+254741120422</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>sales@westkenyasugar.ke</t>
+          <t>info@westkenyasugar.ke</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>laikipia</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L14" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1220,41 +1272,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kevin Kiprotich</t>
+          <t>Peter Wambui</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+254706755674</t>
+          <t>+254797172574</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>orders@mumiassugar.ac.ke</t>
+          <t>support@mumiassugar.co.ke</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L15" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1276,41 +1331,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paul Omondi</t>
+          <t>Brian Cheruiyot</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+254741120422</t>
+          <t>+254793865388</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>info@rahapremium.ke</t>
+          <t>admin@rahapremium.co.ke</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12</v>
+      </c>
+      <c r="M16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1332,41 +1390,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Peter Wambui</t>
+          <t>David Achieng</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+254797172574</t>
+          <t>+254714167136</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>support@bidcoafrica.co.ke</t>
+          <t>orders@bidcoafrica.co.ke</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L17" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,42 +1449,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paul Kimani</t>
+          <t>Peter Otieno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+254713665492</t>
+          <t>+254721174299</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>admin@kapaoilrefineries.ac.ke</t>
+          <t>support@kapaoilrefineries.co.ke.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Ruiru</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1444,12 +1508,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Samuel Muthoni</t>
+          <t>Faith Wambui</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+254707359947</t>
+          <t>+254796526833</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1459,26 +1523,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L19" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1500,41 +1567,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Peter Otieno</t>
+          <t>John Kariuki</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+254714170674</t>
+          <t>+254791455784</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>info@kasukufoods.ke</t>
+          <t>info@kasukufoods.co.ke</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Thika</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L20" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1556,41 +1626,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Victor Ouma</t>
+          <t>Faith Odhiambo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+254740354801</t>
+          <t>+254728947272</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>accounts@execonsumerbrands.ke</t>
+          <t>support@execonsumerbrands.co.ke</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Maua</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L21" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14</v>
+      </c>
+      <c r="M21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1612,41 +1685,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dorcas Otieno</t>
+          <t>Lucy Wambui</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+254768785197</t>
+          <t>+254713520521</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>admin@crownfoods.co.ke</t>
+          <t>info@crownfoods.co.ke</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nyali</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L22" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1668,27 +1744,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brian Chebet</t>
+          <t>Ann Cheruiyot</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+254745570405</t>
+          <t>+254762853305</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>sales@topfryltd.ke</t>
+          <t>accounts@topfryltd.co.ke</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kitengela</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1696,13 +1772,16 @@
           <t>Net 15</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L23" t="b">
+      <c r="J23" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1724,41 +1803,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dennis Wanjiku</t>
+          <t>Joyce Otieno</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+254703783823</t>
+          <t>+254703712554</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>support@riftvalleyproducts.co.ke</t>
+          <t>accounts@riftvalleyproducts.ac.ke</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Athi River</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L24" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1780,12 +1862,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Brian Kariuki</t>
+          <t>Paul Odhiambo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+254703272634</t>
+          <t>+254768346629</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1795,26 +1877,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L25" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11</v>
+      </c>
+      <c r="M25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1836,12 +1921,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dennis Wambui</t>
+          <t>Grace Chebet</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+254709299122</t>
+          <t>+254762850981</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1851,26 +1936,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>11</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L26" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12</v>
+      </c>
+      <c r="M26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1892,12 +1980,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>John Ouma</t>
+          <t>Peter Mwangi</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+254740627276</t>
+          <t>+254729751332</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1907,12 +1995,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1920,13 +2008,16 @@
           <t>Net 7</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>10</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L27" t="b">
+      <c r="J27" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1948,41 +2039,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Faith Kariuki</t>
+          <t>Mary Kamau</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+254707697347</t>
+          <t>+254710559469</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>sales@redbullkenya.ac.ke</t>
+          <t>support@redbullkenya.ac.ke</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Machakos Town</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L28" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12</v>
+      </c>
+      <c r="M28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2004,27 +2098,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Grace Chebet</t>
+          <t>David Wanjiku</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>+254762850981</t>
+          <t>+254792680097</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>orders@monsterenergykenya.co.ke</t>
+          <t>sales@monsterenergykenya.ke</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2032,13 +2126,16 @@
           <t>Net 30</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L29" t="b">
+      <c r="J29" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2060,41 +2157,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Peter Mwangi</t>
+          <t>Lucy Mutua</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+254729751332</t>
+          <t>+254799153266</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>support@delmontekenya.co.ke</t>
+          <t>info@delmontekenya.ac.ke</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L30" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2116,42 +2216,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Faith Maina</t>
+          <t>Grace Kiptoo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>+254718265409</t>
+          <t>+254792563298</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>accounts@keviankenya.ac.ke</t>
+          <t>support@keviankenya.ac.ke</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L31" t="b">
-        <v>0</v>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2172,41 +2275,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>James Cheruiyot</t>
+          <t>John Maina</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>+254719795613</t>
+          <t>+254757679364</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>info@keringetmineralwater.co.ke</t>
+          <t>sales@keringetmineralwater.ke</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L32" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2228,41 +2334,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mercy Nyambura</t>
+          <t>Brian Achieng</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+254713852470</t>
+          <t>+254762207786</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>orders@aquamistltd.co.ke</t>
+          <t>orders@aquamistltd.ac.ke</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>12</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L33" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2284,42 +2393,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Peter Kimani</t>
+          <t>James Kiptoo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>+254798390120</t>
+          <t>+254792448321</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>info@highlandsdrinksltd.co.ke</t>
+          <t>accounts@highlandsdrinksltd.ac.ke</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Meru Town</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L34" t="b">
-        <v>0</v>
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2340,41 +2452,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dennis Kimani</t>
+          <t>John Wambui</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+254746110139</t>
+          <t>+254714309267</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>info@ketepaltd.co.ke</t>
+          <t>accounts@ketepaltd.ke</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Ngong</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L35" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2396,41 +2511,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ann Njoroge</t>
+          <t>Grace Odhiambo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+254702423232</t>
+          <t>+254794392683</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>orders@goldcrownfoods.co.ke</t>
+          <t>orders@goldcrownfoods.ac.ke</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L36" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2452,42 +2570,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paul Njoroge</t>
+          <t>Victor Mutua</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+254715270395</t>
+          <t>+254702213668</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>sales@nestlékenya.ke</t>
+          <t>support@nestlékenya.ke</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Meru Town</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L37" t="b">
-        <v>1</v>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2508,41 +2629,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Grace Kiptoo</t>
+          <t>Victor Chebet</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>+254795835343</t>
+          <t>+254716146542</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>info@dormanscoffee.ke</t>
+          <t>admin@dormanscoffee.ke</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Mombasa CBD</t>
+          <t>Ngong</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L38" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2564,41 +2688,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mercy Achieng</t>
+          <t>David Kamau</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>+254714124813</t>
+          <t>+254742424308</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>admin@javahousecoffee.co.ke</t>
+          <t>admin@javahousecoffee.ke</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L39" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2620,41 +2747,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Samuel Kariuki</t>
+          <t>Kevin Nyambura</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+254768984642</t>
+          <t>+254748415568</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>support@minibakeries.ke</t>
+          <t>accounts@minibakeries.ac.ke</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Nyali</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L40" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2676,17 +2806,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>John Wanjiku</t>
+          <t>Dorcas Muthoni</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>+254758555673</t>
+          <t>+254728808446</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>orders@broadwaysbakery.ac.ke</t>
+          <t>sales@broadwaysbakery.ac.ke</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2701,17 +2831,20 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L41" t="b">
-        <v>0</v>
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2732,42 +2865,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Victor Chebet</t>
+          <t>Peter Achieng</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+254716146542</t>
+          <t>+254768425498</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>admin@farmer'schoice.ke</t>
+          <t>sales@farmer'schoice.co.ke</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L42" t="b">
-        <v>1</v>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2788,27 +2924,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ann Odhiambo</t>
+          <t>Dorcas Kimani</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>+254762446239</t>
+          <t>+254760703634</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>support@kenchicltd.ke</t>
+          <t>sales@kenchicltd.ac.ke</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2816,13 +2952,16 @@
           <t>Cash on Delivery</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L43" t="b">
+      <c r="J43" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2844,41 +2983,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Joyce Kariuki</t>
+          <t>David Kimani</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+254769410016</t>
+          <t>+254714284430</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>support@bradegatepoultry.co.ke</t>
+          <t>admin@bradegatepoultry.ac.ke</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Ruaka</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L44" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2900,41 +3042,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Esther Cheruiyot</t>
+          <t>Dorcas Nyambura</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>+254798100425</t>
+          <t>+254797854213</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>orders@victoryfarms.ke</t>
+          <t>support@victoryfarms.ke</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>8</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L45" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L45" t="n">
+        <v>13</v>
+      </c>
+      <c r="M45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2956,12 +3101,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dorcas Muthoni</t>
+          <t>Faith Mutua</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>+254768324082</t>
+          <t>+254794915451</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2971,26 +3116,29 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>14</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L46" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M46" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3012,17 +3160,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Peter Achieng</t>
+          <t>Grace Omondi</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+254768425498</t>
+          <t>+254720666390</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>sales@bigcoldltd.co.ke</t>
+          <t>info@bigcoldltd.co.ke</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3040,14 +3188,17 @@
           <t>Net 15</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L47" t="b">
-        <v>0</v>
+      <c r="J47" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L47" t="n">
+        <v>13</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3068,41 +3219,44 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Dorcas Kimani</t>
+          <t>Ann Kimani</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+254760703634</t>
+          <t>+254721668969</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>sales@tropicalheatltd.ac.ke</t>
+          <t>accounts@tropicalheatltd.ke</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L48" t="n">
         <v>8</v>
       </c>
-      <c r="K48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L48" t="b">
+      <c r="M48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3124,41 +3278,44 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>David Kimani</t>
+          <t>Victor Kariuki</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+254714284430</t>
+          <t>+254740106182</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>admin@propackkenya.ac.ke</t>
+          <t>orders@propackkenya.ke</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Ruaka</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L49" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10</v>
+      </c>
+      <c r="M49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3180,41 +3337,44 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Daniel Muthoni</t>
+          <t>Lucy Achieng</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+254762656932</t>
+          <t>+254717557007</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>support@kenafricindustries.ac.ke</t>
+          <t>accounts@kenafricindustries.co.ke</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>14</v>
-      </c>
-      <c r="K50" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L50" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L50" t="n">
+        <v>13</v>
+      </c>
+      <c r="M50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3236,41 +3396,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ann Cheruiyot</t>
+          <t>Paul Cheruiyot</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>+254728266889</t>
+          <t>+254701513160</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>admin@perfettivanmelle.ke</t>
+          <t>support@perfettivanmelle.ac.ke</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L51" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L51" t="n">
+        <v>12</v>
+      </c>
+      <c r="M51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3292,27 +3455,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lucy Achieng</t>
+          <t>John Mutua</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>+254717561239</t>
+          <t>+254724443254</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>info@wrigleyeastafrica.ac.ke</t>
+          <t>sales@wrigleyeastafrica.ke</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3320,13 +3483,16 @@
           <t>Net 30</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L52" t="b">
+      <c r="J52" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3348,38 +3514,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Daniel Njoroge</t>
+          <t>Peter Wambui</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>+254714501641</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>+254701885408</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>support@cadburykenya.co.ke</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Nyali</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>5</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L53" t="b">
-        <v>1</v>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L53" t="n">
+        <v>14</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3400,41 +3573,44 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ann Otieno</t>
+          <t>Faith Chebet</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+254713973349</t>
+          <t>+254798121369</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>accounts@reckittbenckiser.ke</t>
+          <t>support@reckittbenckiser.co.ke</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Thika</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>11</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L54" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L54" t="n">
+        <v>12</v>
+      </c>
+      <c r="M54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3456,41 +3632,44 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lucy Mwangi</t>
+          <t>Grace Maina</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>+254722413118</t>
+          <t>+254710735324</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>accounts@pzcussons.ke</t>
+          <t>support@pzcussons.ac.ke</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>bungoma</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L55" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3502,7 +3681,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Colgate Palmolive</t>
+          <t>Colgate Palmolive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3512,41 +3691,44 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Faith Mutua</t>
+          <t>Victor Kariuki</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>+254727609232</t>
+          <t>+254725849747</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>info@colgatepalmolive.ke</t>
+          <t>sales@colgatepalmolive.co.ke</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>NRB</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>12</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L56" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L56" t="n">
+        <v>13</v>
+      </c>
+      <c r="M56" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3568,12 +3750,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Daniel Nyambura</t>
+          <t>Victor Otieno</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>+254745128276</t>
+          <t>+254722658623</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3583,26 +3765,29 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>12</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L57" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3624,41 +3809,44 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kevin Otieno</t>
+          <t>Ann Maina</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>+254716497519</t>
+          <t>+254760968962</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>orders@proctergamblekenya.co.ke</t>
+          <t>accounts@proctergamblekenya.ac.ke</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>7</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L58" t="n">
+        <v>13</v>
+      </c>
+      <c r="M58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3670,7 +3858,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Johnson &amp; Johnson Kenya</t>
+          <t>Johnson &amp; Johnson Kenya</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3680,10 +3868,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Grace Odhiambo</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Dennis Wambui</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+254729556732</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>admin@johnsonjohnsonkenya.ac.ke</t>
@@ -3696,21 +3888,24 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
-      <c r="K59" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L59" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3732,41 +3927,44 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Faith Chebet</t>
+          <t>Dorcas Ouma</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>+254798121369</t>
+          <t>+254759800646</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>support@niveakenya.co.ke</t>
+          <t>accounts@niveakenya.ke</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Thika</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L60" t="n">
         <v>4</v>
       </c>
-      <c r="K60" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L60" t="b">
+      <c r="M60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3788,41 +3986,44 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Grace Maina</t>
+          <t>Joyce Mutua</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>+254710735324</t>
+          <t>+254758835244</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>support@unileverkenya.ac.ke</t>
+          <t>orders@unileverkenya.ac.ke</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Kirinyaga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kerugoya</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L61" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L61" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3844,41 +4045,44 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Victor Mwangi</t>
+          <t>Lucy Wambui</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>+254719703766</t>
+          <t>+254728931450</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>admin@pwanioilproducts.ke</t>
+          <t>info@pwanioilproducts.co.ke</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L62" t="n">
         <v>13</v>
       </c>
-      <c r="K62" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L62" t="b">
+      <c r="M62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3900,41 +4104,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mercy Nyambura</t>
+          <t>Lucy Cheruiyot</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>+254796226935</t>
+          <t>+254743460455</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>support@pyrexkenya.co.ke</t>
+          <t>accounts@pyrexkenya.ac.ke</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>10</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L63" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L63" t="n">
+        <v>13</v>
+      </c>
+      <c r="M63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3956,41 +4163,44 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Joyce Mwangi</t>
+          <t>Faith Wanjiku</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>+254799540463</t>
+          <t>+254791301939</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>accounts@tefalkenya.co.ke</t>
+          <t>orders@tefalkenya.co.ke</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L64" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5</v>
+      </c>
+      <c r="M64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4012,41 +4222,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kevin Kiprotich</t>
+          <t>Victor Kiprotich</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>+254761383201</t>
+          <t>+254758396745</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>support@prestigekenya.ac.ke</t>
+          <t>info@prestigekenya.co.ke</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>9</v>
-      </c>
-      <c r="K65" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L65" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4</v>
+      </c>
+      <c r="M65" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4068,27 +4281,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Joyce Achieng</t>
+          <t>Grace Otieno</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>+254798190872</t>
+          <t>0703680238</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>orders@luminarckenya.ke</t>
+          <t>orders@luminarckenya.ac.ke</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4096,13 +4309,16 @@
           <t>Net 15</t>
         </is>
       </c>
-      <c r="J66" t="n">
-        <v>14</v>
-      </c>
-      <c r="K66" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L66" t="b">
+      <c r="J66" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4124,41 +4340,44 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>James Wambui</t>
+          <t>Dorcas Omondi</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>+254799440802</t>
+          <t>+254711153872</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>sales@royalfordkenya.ke</t>
+          <t>orders@royalfordkenya.ke</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>7</v>
-      </c>
-      <c r="K67" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L67" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L67" t="n">
+        <v>9</v>
+      </c>
+      <c r="M67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4170,7 +4389,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Samsung Electronics Kenya</t>
+          <t xml:space="preserve"> Samsung Electronics Kenya</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4180,41 +4399,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dennis Mwangi</t>
+          <t>Daniel Ouma</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>+254743300337</t>
+          <t>+254719189318</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>info@samsungelectronicskenya.co.ke</t>
+          <t>sales@samsungelectronicskenya.co.ke</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Ruiru</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>8</v>
-      </c>
-      <c r="K68" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L68" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L68" t="n">
+        <v>14</v>
+      </c>
+      <c r="M68" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4236,41 +4458,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Dorcas Mwangi</t>
+          <t>Mercy Ouma</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>+254705408528</t>
+          <t>+254727420214</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>sales@lgelectronicskenya.ke</t>
+          <t>support@lgelectronicskenya.ac.ke</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>5</v>
-      </c>
-      <c r="K69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4292,41 +4517,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ann Cheruiyot</t>
+          <t>Faith Kiptoo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>+254721468900</t>
+          <t>+254746178711</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>admin@sonykenya.ke</t>
+          <t>sales@sonykenya.co.ke</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Machakos Town</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L70" t="n">
         <v>6</v>
       </c>
-      <c r="K70" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L70" t="b">
+      <c r="M70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4348,41 +4576,44 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>David Cheruiyot</t>
+          <t>Dorcas Odhiambo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>+254793823688</t>
+          <t>+254768344762</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>sales@philipskenya.co.ke</t>
+          <t>orders@philipskenya.ac.ke</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>13</v>
-      </c>
-      <c r="K71" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L71" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J71" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4404,41 +4635,44 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paul Kamau</t>
+          <t>Daniel Odhiambo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+254706973074</t>
+          <t>+254703273982</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>sales@ramtonsltd.ke</t>
+          <t>orders@ramtonsltd.ac.ke</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>7</v>
-      </c>
-      <c r="K72" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L72" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L72" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4460,41 +4694,44 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Grace Otieno</t>
+          <t>Grace Kiprotich</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>+254703680238</t>
+          <t>+254745617781</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>orders@vonhotpoint.ac.ke</t>
+          <t>accounts@vonhotpoint.co.ke</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>12</v>
-      </c>
-      <c r="K73" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L73" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L73" t="n">
+        <v>13</v>
+      </c>
+      <c r="M73" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4516,27 +4753,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mercy Wambui</t>
+          <t>Peter Achieng</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>+254740561865</t>
+          <t>+254768976566</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>orders@bickenya.co.ke</t>
+          <t>support@bickenya.ac.ke</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Meru Town</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4544,13 +4781,16 @@
           <t>Net 7</t>
         </is>
       </c>
-      <c r="J74" t="n">
-        <v>6</v>
-      </c>
-      <c r="K74" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L74" t="b">
+      <c r="J74" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L74" t="n">
+        <v>14</v>
+      </c>
+      <c r="M74" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4572,41 +4812,44 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lucy Odhiambo</t>
+          <t>Grace Kiptoo</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>+254748760021</t>
+          <t>+254757557058</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>admin@casiokenya.co.ke</t>
+          <t>admin@casiokenya.ke</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Athi River</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>4</v>
-      </c>
-      <c r="K75" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L75" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J75" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8</v>
+      </c>
+      <c r="M75" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4628,41 +4871,44 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>David Cheruiyot</t>
+          <t>Joyce Kimani</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>+254718265409</t>
+          <t>+254769619536</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>support@officepointkenya.ac.ke</t>
+          <t>orders@officepointkenya.ac.ke</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Machakos Town</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>11</v>
-      </c>
-      <c r="K76" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L76" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4674,7 +4920,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Text Book Centre</t>
+          <t xml:space="preserve"> Text Book Centre </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4684,41 +4930,44 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mercy Ouma</t>
+          <t>Esther Kiprotich</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>+254727420214</t>
+          <t>+254797101206</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>support@textbookcentre.ac.ke</t>
+          <t>admin@textbookcentre.ac.ke</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>11</v>
-      </c>
-      <c r="K77" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L77" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5</v>
+      </c>
+      <c r="M77" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4740,41 +4989,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Grace Odhiambo</t>
+          <t>Dorcas Otieno</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+254710351516</t>
+          <t>+254713380028</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>sales@pedigreekenya.ac.ke</t>
+          <t>support@pedigreekenya.co.ke</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>4</v>
-      </c>
-      <c r="K78" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L78" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L78" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4796,19 +5048,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mercy Otieno</t>
+          <t>Kevin Kamau</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>+254714402099</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>admin@whiskaskenya.ke</t>
-        </is>
-      </c>
+          <t>+254746114338</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>Trans Nzoia</t>
@@ -4821,16 +5069,19 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L79" t="n">
         <v>9</v>
       </c>
-      <c r="K79" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L79" t="b">
+      <c r="M79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4852,41 +5103,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Victor Chebet</t>
+          <t>Mercy Kiprotich</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>+254727220351</t>
+          <t>+254790386706</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>support@purinakenya.co.ke</t>
+          <t>accounts@purinakenya.ke</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Nakuru County</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>4</v>
-      </c>
-      <c r="K80" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L80" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L80" t="n">
+        <v>10</v>
+      </c>
+      <c r="M80" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4908,37 +5162,44 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Kevin Kamau</t>
+          <t>Peter Mutua</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>+254758885339</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>+254794928381</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>accounts@smartheartkenya.ke</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Machakos Town</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L81" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4960,41 +5221,44 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Samuel Cheruiyot</t>
+          <t>Daniel Muthoni</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>+254741559023</t>
+          <t>+254745607868</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>info@freshharvestsuppliers.ac.ke</t>
+          <t>orders@freshharvestsuppliers.ke</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>8</v>
-      </c>
-      <c r="K82" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L82" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L82" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5016,12 +5280,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Faith Ouma</t>
+          <t>Faith Kimani</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>+254757121753</t>
+          <t>+254702433632</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5031,26 +5295,29 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Nairobi CBD</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L83" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L83" t="n">
+        <v>12</v>
+      </c>
+      <c r="M83" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5072,27 +5339,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Dorcas Mutua</t>
+          <t>John Njoroge</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>+254711713762</t>
+          <t>+254742718849</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>accounts@naturefreshltd.ac.ke</t>
+          <t>orders@naturefreshltd.co.ke</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5100,13 +5367,16 @@
           <t>Advance Payment</t>
         </is>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>5</v>
-      </c>
-      <c r="L84" t="b">
+      <c r="J84" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L84" t="n">
+        <v>10</v>
+      </c>
+      <c r="M84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5128,41 +5398,44 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Joyce Wanjiku</t>
+          <t>Daniel Kimani</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>+254799268637</t>
+          <t>+254761261859</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>orders@farmchoicekenya.ke</t>
+          <t>info@ farmchoicekenya.ke</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Nyali</t>
+          <t>Kilimani</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>9</v>
-      </c>
-      <c r="K85" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L85" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L85" t="n">
+        <v>11</v>
+      </c>
+      <c r="M85" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5184,27 +5457,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Dorcas Odhiambo</t>
+          <t>Dennis Kariuki</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>+254720364659</t>
+          <t>+254720757246</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>orders@organicselectkenya.co.ke</t>
+          <t>admin@organicselectkenya.ke</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Athi River</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5212,13 +5485,16 @@
           <t>Advance Payment</t>
         </is>
       </c>
-      <c r="J86" t="n">
-        <v>8</v>
-      </c>
-      <c r="K86" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L86" t="b">
+      <c r="J86" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5230,51 +5506,54 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Brookside Dairy Ltd - Kakamega Branch</t>
+          <t>Dormans Coffee - Nakuru Branch</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Tea &amp; Coffee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ann Otieno</t>
+          <t>David Wanjiku</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>+254712643623</t>
+          <t>+254728274446</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>orders@brooksidedairyltd.ac.ke</t>
+          <t>admin@dormanscoffee.ke</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Athi River</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>9</v>
-      </c>
-      <c r="K87" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L87" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L87" t="n">
+        <v>14</v>
+      </c>
+      <c r="M87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5286,51 +5565,54 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Red Bull Kenya - Eldoret Branch</t>
+          <t>Big Cold Ltd - Meru Branch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Frozen Foods</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mercy Muthoni</t>
+          <t>Faith Kiprotich</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>+254769608257</t>
+          <t>+254726693418</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>info@redbullkenya.co.ke</t>
+          <t>admin@bigcoldltd.co.ke</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Mombasa CBD</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L88" t="n">
         <v>11</v>
       </c>
-      <c r="K88" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L88" t="b">
+      <c r="M88" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5342,51 +5624,54 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Broadways Bakery - Kitale Branch</t>
+          <t>SmartHeart Kenya - Kakamega Branch</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Pet Care</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ann Odhiambo</t>
+          <t>Victor Njoroge</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>+254714982277</t>
+          <t>254714583550</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>info@broadwaysbakery.ke</t>
+          <t>admin@smartheartkenya.ke</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>12</v>
-      </c>
-      <c r="K89" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L89" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L89" t="n">
+        <v>14</v>
+      </c>
+      <c r="M89" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5398,7 +5683,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Java House Coffee - Kitale Branch</t>
+          <t>Dormans Coffee - Kakamega Branch</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5408,27 +5693,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lucy Wambui</t>
+          <t>Peter Muthoni</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>+254715578975</t>
+          <t>+254722716113</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>support@javahousecoffee.co.ke</t>
+          <t>orders@dormanscoffee.ac.ke</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5436,13 +5721,16 @@
           <t>Net 45</t>
         </is>
       </c>
-      <c r="J90" t="n">
-        <v>5</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L90" t="b">
+      <c r="J90" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L90" t="n">
+        <v>6</v>
+      </c>
+      <c r="M90" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5454,51 +5742,54 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rina Industries - Mombasa Branch</t>
+          <t>Perfetti Van Melle - Thika Branch</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Confectionery</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Joyce Kiprotich</t>
+          <t>Esther Ouma</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>+254717960408</t>
+          <t>+254722702733</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>info@rinaindustries.ke</t>
+          <t>orders@perfettivanmelle.ac.ke</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L91" t="b">
+      <c r="M91" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5510,51 +5801,54 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Organic Select Kenya - Thika Branch</t>
+          <t>Delamere Dairy - Machakos Branch</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fresh Produces</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Dennis Wambui</t>
+          <t>Faith Nyambura</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>+254722448588</t>
+          <t>+254796469435</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>support@organicselectkenya.ac.ke</t>
+          <t>sales@delameredairy.ac.ke</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L92" t="b">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L92" t="n">
+        <v>12</v>
+      </c>
+      <c r="M92" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5566,51 +5860,54 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Keringet Mineral Water - Machakos Branch</t>
+          <t>Fresh Harvest Suppliers - Kakamega Branch</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ann Otieno</t>
+          <t>Dorcas Otieno</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>+254720880879</t>
+          <t>+254757482584</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>accounts@keringetmineralwater.ac.ke</t>
+          <t>admin@freshharvestsuppliers.co.ke</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>8</v>
-      </c>
-      <c r="K93" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L93" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J93" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L93" t="n">
+        <v>13</v>
+      </c>
+      <c r="M93" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5622,51 +5919,54 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Farm Choice Kenya - Kisumu Branch</t>
+          <t>Varun Beverages Kenya - Kisumu Branch</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fresh Produce</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Daniel Kiprotich</t>
+          <t>Samuel Kiprotich</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+254757448121</t>
+          <t>+254717970813</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>info@farmchoicekenya.ke</t>
+          <t>sales@varunbeverageskenya.ke</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>10</v>
-      </c>
-      <c r="K94" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L94" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L94" t="n">
+        <v>13</v>
+      </c>
+      <c r="M94" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5678,7 +5978,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kasuku Foods - Nyeri Branch</t>
+          <t>Raha Premium - Thika Branch</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5688,41 +5988,44 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lucy Mutua</t>
+          <t>Faith Kariuki</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>+254721753534</t>
+          <t>+254799943671</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>admin@kasukufoods.ke</t>
+          <t>support@rahapremium.ke</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nakuru Town</t>
+          <t>Machakos Town</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>3</v>
-      </c>
-      <c r="K95" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L95" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L95" t="n">
+        <v>6</v>
+      </c>
+      <c r="M95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5734,51 +6037,54 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sony Kenya - Nyeri Branch</t>
+          <t>Nivea Kenya - Meru Branch</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Dennis Otieno</t>
+          <t>Esther Maina</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+254759171744</t>
+          <t>+254706807617</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>sales@sonykenya.ac.ke</t>
+          <t>sales@niveakenya.ke</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>6</v>
-      </c>
-      <c r="K96" t="n">
-        <v>5</v>
-      </c>
-      <c r="L96" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L96" t="n">
+        <v>12</v>
+      </c>
+      <c r="M96" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5790,51 +6096,54 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GlaxoSmithKline Kenya - Mombasa Branch</t>
+          <t>Unilever Kenya - Kisii Branch</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Health &amp; Pharmacy</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Kevin Kamau</t>
+          <t>David Njoroge</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+254701148225</t>
+          <t>+254702139019</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>orders@glaxosmithklinekenya.co.ke</t>
+          <t>orders@unileverkenya.ke</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>7</v>
-      </c>
-      <c r="K97" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L97" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J97" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L97" t="n">
+        <v>10</v>
+      </c>
+      <c r="M97" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5846,51 +6155,54 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LG Electronics Kenya - Nyeri Branch</t>
+          <t>Nivea Kenya - Meru Branch</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Kevin Kiptoo</t>
+          <t>Victor Njoroge</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>+254705739098</t>
+          <t>+254726786735</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>accounts@lgelectronicskenya.ac.ke</t>
+          <t>info@niveakenya.ke</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>5</v>
-      </c>
-      <c r="K98" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L98" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5902,51 +6214,54 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kevian Kenya - Thika Branch</t>
+          <t>Monster Energy Kenya - Thika Branch</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Juices</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Grace Mwangi</t>
+          <t>Mary Wanjiku</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>+254796587853</t>
+          <t>+254768485178</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>orders@keviankenya.ac.ke</t>
+          <t>support@monsterenergykenya.ac.ke</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>4</v>
-      </c>
-      <c r="K99" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L99" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J99" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L99" t="n">
+        <v>6</v>
+      </c>
+      <c r="M99" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5958,37 +6273,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Text Book Centre - Eldoret Branch</t>
+          <t>Bidco Africa - Thika Branch</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Dorcas Kamau</t>
+          <t>Brian Nyambura</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>+254712503380</t>
+          <t>+254701153035</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>accounts@textbookcentre.co.ke</t>
+          <t>orders@bidcoafrica.co.ke</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Nyali</t>
+          <t>Mlolongo</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5996,13 +6311,16 @@
           <t>Net 15</t>
         </is>
       </c>
-      <c r="J100" t="n">
-        <v>8</v>
-      </c>
-      <c r="K100" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L100" t="b">
+      <c r="J100" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L100" t="n">
+        <v>14</v>
+      </c>
+      <c r="M100" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6014,37 +6332,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Java House Coffee - Nairobi Branch</t>
+          <t>Text Book Centre - Nakuru Branch</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tea &amp; Coffee</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>James Ouma</t>
+          <t>Daniel Nyambura</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>+254748760021</t>
+          <t>+254700390743</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>admin@javahousecoffee.co.ke</t>
+          <t>sales@textbookcentre.co.ke</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6052,13 +6370,16 @@
           <t>Net 60</t>
         </is>
       </c>
-      <c r="J101" t="n">
-        <v>13</v>
-      </c>
-      <c r="K101" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L101" t="b">
+      <c r="J101" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L101" t="n">
+        <v>3</v>
+      </c>
+      <c r="M101" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6070,51 +6391,54 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dormans Coffee - Nakuru Branch</t>
+          <t xml:space="preserve">Kinangop Dairy - Kisumu Branch </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tea &amp; Coffee</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Faith Chebet</t>
+          <t>Faith Ouma</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>+254759362801</t>
+          <t>+254720116547</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>admin@dormanscoffee.ac.ke</t>
+          <t>sales@kinangopdairy.ke</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>12</v>
-      </c>
-      <c r="K102" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L102" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J102" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10</v>
+      </c>
+      <c r="M102" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6126,51 +6450,54 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>West Kenya Sugar - Kakamega Branch</t>
+          <t>Upfield Kenya - Thika Branch</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Dorcas Otieno</t>
+          <t>Samuel Ouma</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+254757482584</t>
+          <t>+254706573962</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>admin@westkenyasugar.co.ke</t>
+          <t>support@upfieldkenya,co.ke</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kiambu Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>6</v>
-      </c>
-      <c r="K103" t="n">
-        <v>4</v>
-      </c>
-      <c r="L103" t="b">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9</v>
+      </c>
+      <c r="M103" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6182,51 +6509,54 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Varun Beverages Kenya - Kisumu Branch</t>
+          <t>Kinangop Dairy - Nairobi Branch</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Samuel Kiprotich</t>
+          <t>Ann Wanjiku</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>+254717970813</t>
+          <t>+254741847006</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>sales@varunbeverageskenya.ke</t>
+          <t>accounts@kinangopdairy.co.ke</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>9</v>
-      </c>
-      <c r="K104" t="n">
-        <v>5</v>
-      </c>
-      <c r="L104" t="b">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J104" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L104" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6238,51 +6568,54 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Victory Farms - Mombasa Branch</t>
+          <t>SmartHeart Kenya - Kakamega Branch</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fish &amp; Seafood</t>
+          <t>Pet Care</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Daniel Achieng</t>
+          <t>Esther Nyambura</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>+254768859396</t>
+          <t>+254743409222</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>admin@victoryfarms.ke</t>
+          <t>accounts@smartheartkenya.ac.ke</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L105" t="n">
         <v>14</v>
       </c>
-      <c r="K105" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L105" t="b">
+      <c r="M105" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6294,51 +6627,54 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wrigley East Africa - Nairobi Branch</t>
+          <t>Farm Choice Kenya - Kakamega Branch</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Confectionery</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>David Muthoni</t>
+          <t>Ann Muthoni</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>+254723805511</t>
+          <t>+254714533914</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>admin@wrigleyeastafrica.ac.ke</t>
+          <t>orders@farmchoicekenya.ke</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>11</v>
-      </c>
-      <c r="K106" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L106" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L106" t="n">
+        <v>7</v>
+      </c>
+      <c r="M106" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6350,51 +6686,54 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Propack Kenya - Mombasa Branch</t>
+          <t>Highlands Drinks Ltd - Meru Branch</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>James Nyambura</t>
+          <t>Lucy Odhiambo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>+254746443939</t>
+          <t>+254705972176</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>support@propackkenya.co.ke</t>
+          <t>info@highlandsdrinksltd.co.ke</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>3</v>
-      </c>
-      <c r="K107" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L107" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J107" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L107" t="n">
+        <v>14</v>
+      </c>
+      <c r="M107" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6406,37 +6745,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mini Bakeries - Kakamega Branch</t>
+          <t>Lato Milk - Machakos Branch</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Daniel Otieno</t>
+          <t>David Kimani</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>+254702419149</t>
+          <t>+254722797660</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>accounts@minibakeries.co.ke</t>
+          <t>accounts@latomilk.ac.ke</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Mombasa CBD</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6444,13 +6783,16 @@
           <t>Net 7</t>
         </is>
       </c>
-      <c r="J108" t="n">
-        <v>5</v>
-      </c>
-      <c r="K108" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L108" t="b">
+      <c r="J108" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L108" t="n">
+        <v>7</v>
+      </c>
+      <c r="M108" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6462,51 +6804,54 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nivea Kenya - Meru Branch</t>
+          <t>Luminarc Kenya - Nakuru Branch</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Victor Njoroge</t>
+          <t>Lucy Achieng</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>+254726786735</t>
+          <t>+254799213475</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>info@niveakenya.ke</t>
+          <t>orders@luminarckenya.ac.ke</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Net 60</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>8</v>
-      </c>
-      <c r="K109" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L109" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J109" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L109" t="n">
+        <v>11</v>
+      </c>
+      <c r="M109" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6518,51 +6863,54 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Propack Kenya - Nakuru Branch</t>
+          <t>Colgate Palmolive - Kitale Branch</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Faith Maina</t>
+          <t>Paul Mutua</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>+254706818987</t>
+          <t>+254701289179</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>orders@propackkenya.ac.ke</t>
+          <t>orders@colgatepalmolive.ac.ke</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>kilifi</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L110" t="n">
         <v>7</v>
       </c>
-      <c r="K110" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L110" t="b">
+      <c r="M110" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6574,7 +6922,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bidco Africa - Thika Branch</t>
+          <t>Kasuku Foods - Machakos Branch</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6584,41 +6932,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Brian Nyambura</t>
+          <t>Daniel Mwangi</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>+254701153035</t>
+          <t>+254705882354</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>orders@bidcoafrica.co.ke</t>
+          <t>support@kasukufoods.co.ke</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Mlolongo</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Net 15</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>14</v>
-      </c>
-      <c r="K111" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L111" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L111" t="n">
+        <v>7</v>
+      </c>
+      <c r="M111" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6630,51 +6981,54 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ramtons Ltd - Nakuru Branch</t>
+          <t>Broadways Bakery - Kisii Branch</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Faith Omondi</t>
+          <t>John Njoroge</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>+254794254721</t>
+          <t>+254710891083</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>support@ramtonsltd.co.ke</t>
+          <t>support@broadwaysbakery.co.ke</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>4</v>
-      </c>
-      <c r="K112" t="n">
-        <v>5</v>
-      </c>
-      <c r="L112" t="b">
+          <t>Cash on Delivery</t>
+        </is>
+      </c>
+      <c r="J112" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L112" t="n">
+        <v>9</v>
+      </c>
+      <c r="M112" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6686,51 +7040,54 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rift Valley Products - Mombasa Branch</t>
+          <t>Tefal Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>James Maina</t>
+          <t>Grace Chebet</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>+254795926730</t>
+          <t>+254793637234</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>sales@riftvalleyproducts.ac.ke</t>
+          <t>info@tefalkenya.ke</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Westlands</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>2</v>
-      </c>
-      <c r="K113" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L113" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J113" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L113" t="n">
+        <v>12</v>
+      </c>
+      <c r="M113" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6742,51 +7099,54 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PZ Cussons - Kitale Branch</t>
+          <t>Tefal Kenya - Kitale Branch</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Multiple</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Lucy Muthoni</t>
+          <t>Faith Kariuki</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>+254794479625</t>
+          <t>+254758157443</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>support@pzcussons.ac.ke</t>
+          <t>info@tefalkenya.co.ke</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kitengela</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>9</v>
-      </c>
-      <c r="K114" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L114" t="b">
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J114" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K114" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L114" t="n">
+        <v>14</v>
+      </c>
+      <c r="M114" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6798,51 +7158,54 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Happy Cow Ltd - Kisii Branch</t>
+          <t>Kenchic Ltd - Mombasa Branch</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Meat &amp; Poultry</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Mercy Muthoni</t>
+          <t>Ann Kiptoo</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>+254761132663</t>
+          <t>+254708498676</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>info@happycowltd.ke</t>
+          <t>support@kenchicltd.ac.ke</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nyandarua</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kasarani</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J115" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K115" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L115" t="n">
         <v>8</v>
       </c>
-      <c r="K115" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L115" t="b">
+      <c r="M115" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6854,37 +7217,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Kenya - Mombasa Branch</t>
+          <t>Happy Cow Ltd - Nyeri Branch</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paul Njoroge</t>
+          <t>Peter Omondi</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>+254704232321</t>
+          <t>+254748550137</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>orders@proctergamblekenya.ac.ke</t>
+          <t>support@happycowltd.ke</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Athi River</t>
+          <t>Kasarani</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6892,13 +7255,16 @@
           <t>Cash on Delivery</t>
         </is>
       </c>
-      <c r="J116" t="n">
-        <v>11</v>
-      </c>
-      <c r="K116" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L116" t="b">
+      <c r="J116" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L116" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6910,51 +7276,54 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pedigree Kenya - Kitale Branch</t>
+          <t>Kenchic Ltd - Kisumu Branch</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pet Care</t>
+          <t>Meat &amp; Poultry</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Samuel Nyambura</t>
+          <t>Mary Odhiambo</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>+254727203996</t>
+          <t>+254727985506</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>admin@pedigreekenya.co.ke</t>
+          <t>info@kenchicltd.co.ke</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>12</v>
-      </c>
-      <c r="K117" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L117" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J117" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L117" t="n">
+        <v>8</v>
+      </c>
+      <c r="M117" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6966,52 +7335,55 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Monster Energy Kenya - Nyeri Branch</t>
+          <t>Victory Farms - Nakuru Branch</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Fish &amp; Seafood</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ann Omondi</t>
+          <t>Peter Kiprotich</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>+254797575528</t>
+          <t>+254760219565</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>accounts@monsterenergykenya.ke</t>
+          <t>support@victoryfarms.ac.ke</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>3</v>
-      </c>
-      <c r="K118" t="n">
-        <v>4</v>
-      </c>
-      <c r="L118" t="b">
-        <v>1</v>
+          <t>Net 15</t>
+        </is>
+      </c>
+      <c r="J118" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K118" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L118" t="n">
+        <v>13</v>
+      </c>
+      <c r="M118" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7022,51 +7394,54 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Highlands Drinks Ltd - Meru Branch</t>
+          <t>Nature Fresh Ltd - Kisumu Branch</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lucy Odhiambo</t>
+          <t>Daniel Mutua</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>+254705972176</t>
+          <t>+254712281926</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>info@highlandsdrinksltd.co.ke</t>
+          <t>support@naturefreshltd.co.ke</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>3</v>
-      </c>
-      <c r="K119" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L119" t="b">
+          <t>Advance Payment</t>
+        </is>
+      </c>
+      <c r="J119" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L119" t="n">
+        <v>14</v>
+      </c>
+      <c r="M119" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7078,51 +7453,54 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kapa Oil Refineries - Kitale Branch</t>
+          <t>Unilever Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>David Kimani</t>
+          <t>Victor Nyambura</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+254722797660</t>
+          <t>+254720757685</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>accounts@kapaoilrefineries.ac.ke</t>
+          <t>orders@unileverkenya.co.ke</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kiambu Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Net 7</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>6</v>
-      </c>
-      <c r="K120" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L120" t="b">
+          <t>Net 45</t>
+        </is>
+      </c>
+      <c r="J120" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K120" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L120" t="n">
+        <v>9</v>
+      </c>
+      <c r="M120" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7134,53 +7512,75 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Casio Kenya - Kitale Branch</t>
+          <t>Nestlé Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Tea &amp; Coffee</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lucy Achieng</t>
+          <t>Samuel Odhiambo</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>+254799213475</t>
+          <t>+254719584172</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>orders@casiokenya.ac.ke</t>
+          <t>accounts@nestlékenya.co.ke</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Net 30</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
+          <t>Net 7</t>
+        </is>
+      </c>
+      <c r="J121" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="L121" t="n">
         <v>3</v>
       </c>
-      <c r="K121" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L121" t="b">
-        <v>1</v>
-      </c>
+      <c r="M121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>+254793637234</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/generator/output/master/suppliers.xlsx
+++ b/generator/output/master/suppliers.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,32 +505,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Grace Achieng</t>
+          <t>Mercy Odhiambo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+254714246316</t>
+          <t>+254799344098</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>admin@brooksidedairyltd.co.ke</t>
+          <t>info@brooksidedairyltd.ke</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kitengela</t>
+          <t>Ruiru</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J2" s="1" t="n">
@@ -540,7 +540,7 @@
         <v>46022</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -564,17 +564,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Samuel Nyambura</t>
+          <t>Peter Nyambura</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+254701688508</t>
+          <t>+254760279451</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>sales@sameeragriculture.ac.ke</t>
+          <t>support@sameeragriculture.ac.ke</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
@@ -599,7 +599,7 @@
         <v>46022</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -623,32 +623,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kevin Kimani</t>
+          <t>Joyce Otieno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+254721391369</t>
+          <t>+254714961722</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>sales@newkcc.co.ke</t>
+          <t>info@newkcc.ke</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ruaka</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
@@ -658,7 +658,7 @@
         <v>46022</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -682,32 +682,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paul Mutua</t>
+          <t>Brian Wambui</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+254796145561</t>
+          <t>+254725774079</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>admin@kinangopdairy.ke</t>
+          <t>accounts@kinangopdairy.co.ke</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
@@ -717,7 +717,7 @@
         <v>46022</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -741,27 +741,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Victor Chebet</t>
+          <t>Victor Kimani</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+254790172933</t>
+          <t>+254757518801</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>info@githunguridairy.ac.ke</t>
+          <t>orders@githunguridairy.co.ke</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -776,7 +776,7 @@
         <v>46022</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -800,32 +800,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dorcas Maina</t>
+          <t>Kevin Kimani</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>254710488162</t>
+          <t>+254758166613</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>orders@happycowltd.co.ke</t>
+          <t>accounts@happycowltd.ke</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
@@ -835,7 +835,7 @@
         <v>46022</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -859,32 +859,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kevin Muthoni</t>
+          <t>David Cheruiyot</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+254724383060</t>
+          <t>+254793379786</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>admin@delameredairy.ac.ke</t>
+          <t>admin@delameredairy.ke</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Kilimani</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
@@ -894,7 +894,7 @@
         <v>46022</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -918,32 +918,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Joyce Kariuki</t>
+          <t>Kevin Kiprotich</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+254717169403</t>
+          <t>+254706755674</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>sales@latomilk.ac.ke</t>
+          <t>orders@latomilk.ac.ke</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
@@ -953,7 +953,7 @@
         <v>46022</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -977,32 +977,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grace Njoroge</t>
+          <t>Paul Omondi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+254715881177</t>
+          <t>+254741120422</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>support@upfieldkenya.ac.ke</t>
+          <t>info@upfieldkenya.ke</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
@@ -1012,7 +1012,7 @@
         <v>46022</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -1036,32 +1036,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lucy Odhiambo</t>
+          <t>Peter Wambui</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+254793149405</t>
+          <t>+254797172574</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>info@ungagroup.co.ke</t>
+          <t>support@ungagroup.co.ke</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
@@ -1071,7 +1071,7 @@
         <v>46022</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -1095,32 +1095,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Samuel Mutua</t>
+          <t>Brian Cheruiyot</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+254746112038</t>
+          <t>+254793865388</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>admin@capwellindustries.ac.ke</t>
+          <t>admin@capwellindustries.co.ke</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
@@ -1130,7 +1130,7 @@
         <v>46022</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -1154,32 +1154,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>James Mutua</t>
+          <t>David Achieng</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+254742898975</t>
+          <t>+254714167136</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>sales@pembeflourmills.ac.ke</t>
+          <t>orders@pembeflourmills.co.ke</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
@@ -1189,7 +1189,7 @@
         <v>46022</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -1213,32 +1213,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paul Omondi</t>
+          <t>Peter Otieno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+254741120422</t>
+          <t>+254721174299</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>info@westkenyasugar.ke</t>
+          <t>support@westkenyasugar.co.ke</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Ruiru</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
@@ -1248,7 +1248,7 @@
         <v>46022</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -1272,17 +1272,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Peter Wambui</t>
+          <t>Faith Wambui</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+254797172574</t>
+          <t>+254796526833</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>support@mumiassugar.co.ke</t>
+          <t>sales@mumiassugar.co.ke</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
@@ -1307,7 +1307,7 @@
         <v>46022</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brian Cheruiyot</t>
+          <t>John Kariuki</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+254793865388</t>
+          <t>+254791455784</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>admin@rahapremium.co.ke</t>
+          <t>info@rahapremium.co.ke</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Thika</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
@@ -1366,7 +1366,7 @@
         <v>46022</v>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -1390,32 +1390,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>David Achieng</t>
+          <t>Faith Odhiambo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+254714167136</t>
+          <t>+254728947272</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>orders@bidcoafrica.co.ke</t>
+          <t>support@bidcoafrica.co.ke</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Maua</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
@@ -1425,7 +1425,7 @@
         <v>46022</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1449,32 +1449,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Peter Otieno</t>
+          <t>Lucy Wambui</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+254721174299</t>
+          <t>+254713520521</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>support@kapaoilrefineries.co.ke.</t>
+          <t>info@kapaoilrefineries.co.ke</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ruiru</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
@@ -1484,7 +1484,7 @@
         <v>46022</v>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -1508,32 +1508,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Faith Wambui</t>
+          <t>Ann Cheruiyot</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+254796526833</t>
+          <t>+254762853305</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>sales@rinaindustries.co.ke</t>
+          <t>accounts@rinaindustries.co.ke</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J19" s="1" t="n">
@@ -1543,7 +1543,7 @@
         <v>46022</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>John Kariuki</t>
+          <t>Joyce Otieno</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+254791455784</t>
+          <t>+254703712554</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>info@kasukufoods.co.ke</t>
+          <t>accounts@kasukufoods.ac.ke</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Thika</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
@@ -1602,7 +1602,7 @@
         <v>46022</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -1626,32 +1626,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Faith Odhiambo</t>
+          <t>Paul Odhiambo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+254728947272</t>
+          <t>+254768346629</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>support@execonsumerbrands.co.ke</t>
+          <t>accounts@execonsumerbrands.co.ke</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maua</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J21" s="1" t="n">
@@ -1661,7 +1661,7 @@
         <v>46022</v>
       </c>
       <c r="L21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -1685,32 +1685,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lucy Wambui</t>
+          <t>Grace Chebet</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+254713520521</t>
+          <t>+254762850981</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>info@crownfoods.co.ke</t>
+          <t>orders@crownfoods.co.ke</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
@@ -1720,7 +1720,7 @@
         <v>46022</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ann Cheruiyot</t>
+          <t>Peter Mwangi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+254762853305</t>
+          <t>+254729751332</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>accounts@topfryltd.co.ke</t>
+          <t>support@topfryltd.co.ke</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J23" s="1" t="n">
@@ -1779,7 +1779,7 @@
         <v>46022</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Joyce Otieno</t>
+          <t>Mary Kamau</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+254703712554</t>
+          <t>+254710559469</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>accounts@riftvalleyproducts.ac.ke</t>
+          <t>support@riftvalleyproducts.ac.ke</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Machakos Town</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J24" s="1" t="n">
@@ -1838,7 +1838,7 @@
         <v>46022</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M24" t="b">
         <v>1</v>
@@ -1862,32 +1862,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paul Odhiambo</t>
+          <t>David Wanjiku</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+254768346629</t>
+          <t>+254792680097</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>accounts@kensaltltd.co.ke</t>
+          <t>sales@kensaltltd.ke</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J25" s="1" t="n">
@@ -1897,7 +1897,7 @@
         <v>46022</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -1921,32 +1921,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Grace Chebet</t>
+          <t>Lucy Mutua</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+254762850981</t>
+          <t>+254799153266</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>orders@coca-colabeverageskenya.co.ke</t>
+          <t>info@coca-colabeverageskenya.ac.ke</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
@@ -1956,7 +1956,7 @@
         <v>46022</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M26" t="b">
         <v>1</v>
@@ -1980,32 +1980,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Peter Mwangi</t>
+          <t>Grace Kiptoo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+254729751332</t>
+          <t>+254792563298</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>support@varunbeverageskenya.co.ke</t>
+          <t>support@varunbeverageskenya.ac.ke</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J27" s="1" t="n">
@@ -2015,7 +2015,7 @@
         <v>46022</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -2039,32 +2039,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mary Kamau</t>
+          <t>John Maina</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+254710559469</t>
+          <t>+254757679364</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>support@redbullkenya.ac.ke</t>
+          <t>sales@redbullkenya.ke</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Machakos Town</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J28" s="1" t="n">
@@ -2074,7 +2074,7 @@
         <v>46022</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M28" t="b">
         <v>1</v>
@@ -2098,32 +2098,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>David Wanjiku</t>
+          <t>Brian Achieng</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>+254792680097</t>
+          <t>+254762207786</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>sales@monsterenergykenya.ke</t>
+          <t>orders@monsterenergykenya.ac.ke</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J29" s="1" t="n">
@@ -2157,32 +2157,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lucy Mutua</t>
+          <t>James Kiptoo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+254799153266</t>
+          <t>+254792448321</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>info@delmontekenya.ac.ke</t>
+          <t>accounts@delmontekenya.ac.ke</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J30" s="1" t="n">
@@ -2192,7 +2192,7 @@
         <v>46022</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" t="b">
         <v>1</v>
@@ -2216,32 +2216,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Grace Kiptoo</t>
+          <t>John Wambui</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>+254792563298</t>
+          <t>+254714309267</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>support@keviankenya.ac.ke</t>
+          <t>accounts@keviankenya.ke</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Ngong</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J31" s="1" t="n">
@@ -2251,7 +2251,7 @@
         <v>46022</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M31" t="b">
         <v>1</v>
@@ -2275,32 +2275,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>John Maina</t>
+          <t>Grace Odhiambo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>+254757679364</t>
+          <t>+254794392683</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>sales@keringetmineralwater.ke</t>
+          <t>orders@keringetmineralwater.ac.ke</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J32" s="1" t="n">
@@ -2310,7 +2310,7 @@
         <v>46022</v>
       </c>
       <c r="L32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -2334,32 +2334,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Brian Achieng</t>
+          <t>Victor Mutua</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+254762207786</t>
+          <t>+254702213668</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>orders@aquamistltd.ac.ke</t>
+          <t>support@aquamistltd.ke</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kiambu Town</t>
+          <t>Meru Town</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J33" s="1" t="n">
@@ -2369,10 +2369,10 @@
         <v>46022</v>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2393,32 +2393,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>James Kiptoo</t>
+          <t>Victor Chebet</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>+254792448321</t>
+          <t>+254716146542</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>accounts@highlandsdrinksltd.ac.ke</t>
+          <t>admin@highlandsdrinksltd.ke</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Ngong</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J34" s="1" t="n">
@@ -2428,7 +2428,7 @@
         <v>46022</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
@@ -2452,27 +2452,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>John Wambui</t>
+          <t>David Kamau</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+254714309267</t>
+          <t>+254742424308</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>accounts@ketepaltd.ke</t>
+          <t>admin@ketepaltd.ke</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2487,7 +2487,7 @@
         <v>46022</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M35" t="b">
         <v>1</v>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Grace Odhiambo</t>
+          <t>Kevin Nyambura</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+254794392683</t>
+          <t>+254748415568</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>orders@goldcrownfoods.ac.ke</t>
+          <t>accounts@goldcrownfoods.ac.ke</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Nyali</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J36" s="1" t="n">
@@ -2546,7 +2546,7 @@
         <v>46022</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M36" t="b">
         <v>1</v>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Victor Mutua</t>
+          <t>Dorcas Muthoni</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+254702213668</t>
+          <t>+254728808446</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>support@nestlékenya.ke</t>
+          <t>sales@nestlékenya.ac.ke</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Meru Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J37" s="1" t="n">
@@ -2605,10 +2605,10 @@
         <v>46022</v>
       </c>
       <c r="L37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2629,32 +2629,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Victor Chebet</t>
+          <t>Peter Achieng</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>+254716146542</t>
+          <t>+254768425498</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>admin@dormanscoffee.ke</t>
+          <t>sales@dormanscoffee.co.ke</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ngong</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J38" s="1" t="n">
@@ -2664,10 +2664,10 @@
         <v>46022</v>
       </c>
       <c r="L38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2688,32 +2688,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>David Kamau</t>
+          <t>Dorcas Kimani</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>+254742424308</t>
+          <t>+254760703634</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>admin@javahousecoffee.ke</t>
+          <t>sales@javahousecoffee.ac.ke</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J39" s="1" t="n">
@@ -2723,7 +2723,7 @@
         <v>46022</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -2747,32 +2747,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kevin Nyambura</t>
+          <t>David Kimani</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+254748415568</t>
+          <t>+254714284430</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>accounts@minibakeries.ac.ke</t>
+          <t>admin@minibakeries.ac.ke</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nyali</t>
+          <t>Ruaka</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J40" s="1" t="n">
@@ -2782,7 +2782,7 @@
         <v>46022</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M40" t="b">
         <v>1</v>
@@ -2806,32 +2806,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Dorcas Muthoni</t>
+          <t>Dorcas Nyambura</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>+254728808446</t>
+          <t>+254797854213</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>sales@broadwaysbakery.ac.ke</t>
+          <t>support@broadwaysbakery.ke</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J41" s="1" t="n">
@@ -2841,7 +2841,7 @@
         <v>46022</v>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
@@ -2865,32 +2865,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Peter Achieng</t>
+          <t>Faith Mutua</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+254768425498</t>
+          <t>+254794915451</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>sales@farmer'schoice.co.ke</t>
+          <t>support@farmer'schoice.ke</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J42" s="1" t="n">
@@ -2900,10 +2900,10 @@
         <v>46022</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2924,32 +2924,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dorcas Kimani</t>
+          <t>Grace Omondi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>+254760703634</t>
+          <t>+254720666390</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>sales@kenchicltd.ac.ke</t>
+          <t>info@kenchicltd.co.ke</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J43" s="1" t="n">
@@ -2959,7 +2959,7 @@
         <v>46022</v>
       </c>
       <c r="L43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
@@ -2983,32 +2983,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>David Kimani</t>
+          <t>Ann Kimani</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+254714284430</t>
+          <t>+254721668969</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>admin@bradegatepoultry.ac.ke</t>
+          <t>accounts@bradegatepoultry.ke</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ruaka</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J44" s="1" t="n">
@@ -3018,7 +3018,7 @@
         <v>46022</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M44" t="b">
         <v>1</v>
@@ -3042,27 +3042,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Dorcas Nyambura</t>
+          <t>Victor Kariuki</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>+254797854213</t>
+          <t>+254740106182</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>support@victoryfarms.ke</t>
+          <t>orders@victoryfarms.ke</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3077,7 +3077,7 @@
         <v>46022</v>
       </c>
       <c r="L45" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M45" t="b">
         <v>1</v>
@@ -3101,32 +3101,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Faith Mutua</t>
+          <t>Lucy Achieng</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>+254794915451</t>
+          <t>+254717557007</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>support@seaharvestkenya.ke</t>
+          <t>accounts@seaharvestkenya.co.ke</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J46" s="1" t="n">
@@ -3136,7 +3136,7 @@
         <v>46022</v>
       </c>
       <c r="L46" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M46" t="b">
         <v>1</v>
@@ -3160,32 +3160,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Grace Omondi</t>
+          <t>Paul Cheruiyot</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+254720666390</t>
+          <t>+254701513160</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>info@bigcoldltd.co.ke</t>
+          <t>support@bigcoldltd.ac.ke</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J47" s="1" t="n">
@@ -3195,7 +3195,7 @@
         <v>46022</v>
       </c>
       <c r="L47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ann Kimani</t>
+          <t>John Mutua</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+254721668969</t>
+          <t>+254724443254</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>accounts@tropicalheatltd.ke</t>
+          <t>sales@tropicalheatltd.ke</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J48" s="1" t="n">
@@ -3254,7 +3254,7 @@
         <v>46022</v>
       </c>
       <c r="L48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
@@ -3278,32 +3278,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Victor Kariuki</t>
+          <t>Peter Wambui</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+254740106182</t>
+          <t>+254701885408</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>orders@propackkenya.ke</t>
+          <t>support@propackkenya.co.ke</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Nyali</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J49" s="1" t="n">
@@ -3313,10 +3313,10 @@
         <v>46022</v>
       </c>
       <c r="L49" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lucy Achieng</t>
+          <t>Faith Chebet</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+254717557007</t>
+          <t>+254798121369</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>accounts@kenafricindustries.co.ke</t>
+          <t>support@kenafricindustries.co.ke</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Thika</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J50" s="1" t="n">
@@ -3372,7 +3372,7 @@
         <v>46022</v>
       </c>
       <c r="L50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paul Cheruiyot</t>
+          <t>Grace Maina</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>+254701513160</t>
+          <t>+254710735324</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3431,7 +3431,7 @@
         <v>46022</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
@@ -3455,32 +3455,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>John Mutua</t>
+          <t>Victor Kariuki</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>+254724443254</t>
+          <t>+254725849747</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>sales@wrigleyeastafrica.ke</t>
+          <t>sales@wrigleyeastafrica.co.ke</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J52" s="1" t="n">
@@ -3490,7 +3490,7 @@
         <v>46022</v>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M52" t="b">
         <v>1</v>
@@ -3514,27 +3514,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Peter Wambui</t>
+          <t>Victor Otieno</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>+254701885408</t>
+          <t>+254722658623</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>support@cadburykenya.co.ke</t>
+          <t>accounts@cadburykenya.ac.ke</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Nyali</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3549,10 +3549,10 @@
         <v>46022</v>
       </c>
       <c r="L53" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3573,27 +3573,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Faith Chebet</t>
+          <t>Ann Maina</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+254798121369</t>
+          <t>+254760968962</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>support@reckittbenckiser.co.ke</t>
+          <t>accounts@reckittbenckiser.ac.ke</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Thika</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3608,7 +3608,7 @@
         <v>46022</v>
       </c>
       <c r="L54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
@@ -3632,32 +3632,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Grace Maina</t>
+          <t>Dennis Wambui</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>+254710735324</t>
+          <t>+254729556732</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>support@pzcussons.ac.ke</t>
+          <t>admin@pzcussons.ac.ke</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J55" s="1" t="n">
@@ -3667,7 +3667,7 @@
         <v>46022</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
@@ -3691,32 +3691,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Victor Kariuki</t>
+          <t>Dorcas Ouma</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>+254725849747</t>
+          <t>+254759800646</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>sales@colgatepalmolive.co.ke</t>
+          <t>accounts@colgatepalmolive.ke</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NRB</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J56" s="1" t="n">
@@ -3726,7 +3726,7 @@
         <v>46022</v>
       </c>
       <c r="L56" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Victor Otieno</t>
+          <t>Joyce Mutua</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>+254722658623</t>
+          <t>+254758835244</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>accounts@glaxosmithklinekenya.ac.ke</t>
+          <t>orders@glaxosmithklinekenya.ac.ke</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kirinyaga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Kerugoya</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J57" s="1" t="n">
@@ -3785,7 +3785,7 @@
         <v>46022</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ann Maina</t>
+          <t>Lucy Wambui</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>+254760968962</t>
+          <t>+254728931450</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>accounts@proctergamblekenya.ac.ke</t>
+          <t>info@proctergamblekenya.co.ke</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J58" s="1" t="n">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dennis Wambui</t>
+          <t>Lucy Cheruiyot</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>+254729556732</t>
+          <t>+254743460455</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>admin@johnsonjohnsonkenya.ac.ke</t>
+          <t>accounts@johnsonjohnsonkenya.ac.ke</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J59" s="1" t="n">
@@ -3903,7 +3903,7 @@
         <v>46022</v>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -3927,32 +3927,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dorcas Ouma</t>
+          <t>Faith Wanjiku</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>+254759800646</t>
+          <t>+254791301939</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>accounts@niveakenya.ke</t>
+          <t>orders@niveakenya.co.ke</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J60" s="1" t="n">
@@ -3962,7 +3962,7 @@
         <v>46022</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60" t="b">
         <v>1</v>
@@ -3986,32 +3986,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Joyce Mutua</t>
+          <t>Victor Kiprotich</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>+254758835244</t>
+          <t>+254758396745</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>orders@unileverkenya.ac.ke</t>
+          <t>info@unileverkenya.co.ke</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kirinyaga</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kerugoya</t>
+          <t>Makutano</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J61" s="1" t="n">
@@ -4021,7 +4021,7 @@
         <v>46022</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61" t="b">
         <v>1</v>
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lucy Wambui</t>
+          <t>Grace Otieno</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>+254728931450</t>
+          <t>+254703680238</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>info@pwanioilproducts.co.ke</t>
+          <t>orders@pwanioilproducts.ac.ke</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J62" s="1" t="n">
@@ -4080,7 +4080,7 @@
         <v>46022</v>
       </c>
       <c r="L62" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M62" t="b">
         <v>1</v>
@@ -4104,32 +4104,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lucy Cheruiyot</t>
+          <t>Dorcas Omondi</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>+254743460455</t>
+          <t>+254711153872</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>accounts@pyrexkenya.ac.ke</t>
+          <t>orders@pyrexkenya.ke</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J63" s="1" t="n">
@@ -4139,7 +4139,7 @@
         <v>46022</v>
       </c>
       <c r="L63" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M63" t="b">
         <v>1</v>
@@ -4163,32 +4163,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Faith Wanjiku</t>
+          <t>Daniel Ouma</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>+254791301939</t>
+          <t>+254719189318</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>orders@tefalkenya.co.ke</t>
+          <t>sales@tefalkenya.co.ke</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Ruiru</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J64" s="1" t="n">
@@ -4198,7 +4198,7 @@
         <v>46022</v>
       </c>
       <c r="L64" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M64" t="b">
         <v>1</v>
@@ -4222,32 +4222,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Victor Kiprotich</t>
+          <t>Mercy Ouma</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>+254758396745</t>
+          <t>+254727420214</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>info@prestigekenya.co.ke</t>
+          <t>support@prestigekenya.ac.ke</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J65" s="1" t="n">
@@ -4257,7 +4257,7 @@
         <v>46022</v>
       </c>
       <c r="L65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
@@ -4281,32 +4281,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Grace Otieno</t>
+          <t>Faith Kiptoo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0703680238</t>
+          <t>+254746178711</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>orders@luminarckenya.ac.ke</t>
+          <t>sales@luminarckenya.co.ke</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Machakos Town</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J66" s="1" t="n">
@@ -4316,7 +4316,7 @@
         <v>46022</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>1</v>
@@ -4340,32 +4340,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dorcas Omondi</t>
+          <t>Dorcas Odhiambo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>+254711153872</t>
+          <t>+254768344762</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>orders@royalfordkenya.ke</t>
+          <t>orders@royalfordkenya.ac.ke</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J67" s="1" t="n">
@@ -4375,7 +4375,7 @@
         <v>46022</v>
       </c>
       <c r="L67" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Samsung Electronics Kenya</t>
+          <t>Samsung Electronics Kenya</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4399,32 +4399,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Daniel Ouma</t>
+          <t>Daniel Odhiambo</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>+254719189318</t>
+          <t>+254703273982</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>sales@samsungelectronicskenya.co.ke</t>
+          <t>orders@samsungelectronicskenya.ac.ke</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ruiru</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J68" s="1" t="n">
@@ -4434,7 +4434,7 @@
         <v>46022</v>
       </c>
       <c r="L68" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -4458,32 +4458,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mercy Ouma</t>
+          <t>Grace Kiprotich</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>+254727420214</t>
+          <t>+254745617781</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>support@lgelectronicskenya.ac.ke</t>
+          <t>accounts@lgelectronicskenya.co.ke</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J69" s="1" t="n">
@@ -4493,7 +4493,7 @@
         <v>46022</v>
       </c>
       <c r="L69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -4517,32 +4517,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Faith Kiptoo</t>
+          <t>Peter Achieng</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>+254746178711</t>
+          <t>+254768976566</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>sales@sonykenya.co.ke</t>
+          <t>support@sonykenya.ac.ke</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Machakos Town</t>
+          <t>Meru Town</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J70" s="1" t="n">
@@ -4552,7 +4552,7 @@
         <v>46022</v>
       </c>
       <c r="L70" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -4576,32 +4576,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dorcas Odhiambo</t>
+          <t>Grace Kiptoo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>+254768344762</t>
+          <t>+254757557058</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>orders@philipskenya.ac.ke</t>
+          <t>admin@philipskenya.ke</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Kwale</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J71" s="1" t="n">
@@ -4611,7 +4611,7 @@
         <v>46022</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M71" t="b">
         <v>1</v>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Daniel Odhiambo</t>
+          <t>Joyce Kimani</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+254703273982</t>
+          <t>+254769619536</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J72" s="1" t="n">
@@ -4694,32 +4694,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Grace Kiprotich</t>
+          <t>Esther Kiprotich</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>+254745617781</t>
+          <t>+254797101206</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>accounts@vonhotpoint.co.ke</t>
+          <t>admin@vonhotpoint.ac.ke</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J73" s="1" t="n">
@@ -4729,7 +4729,7 @@
         <v>46022</v>
       </c>
       <c r="L73" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M73" t="b">
         <v>1</v>
@@ -4753,32 +4753,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Peter Achieng</t>
+          <t>Dorcas Otieno</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>+254768976566</t>
+          <t>+254713380028</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>support@bickenya.ac.ke</t>
+          <t>support@bickenya.co.ke</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Meru Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J74" s="1" t="n">
@@ -4788,7 +4788,7 @@
         <v>46022</v>
       </c>
       <c r="L74" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
@@ -4812,27 +4812,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Grace Kiptoo</t>
+          <t>Kevin Kamau</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>+254757557058</t>
+          <t>+254746114338</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>admin@casiokenya.ke</t>
+          <t>support@casiokenya.ke</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4847,7 +4847,7 @@
         <v>46022</v>
       </c>
       <c r="L75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M75" t="b">
         <v>1</v>
@@ -4871,27 +4871,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Joyce Kimani</t>
+          <t>Mercy Kiprotich</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>+254769619536</t>
+          <t>+254790386706</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>orders@officepointkenya.ac.ke</t>
+          <t>accounts@officepointkenya.ke</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kitengela</t>
+          <t>Naivasha</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>46022</v>
       </c>
       <c r="L76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M76" t="b">
         <v>1</v>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Text Book Centre </t>
+          <t>Text Book Centre</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Esther Kiprotich</t>
+          <t>Peter Mutua</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>+254797101206</t>
+          <t>+254794928381</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>admin@textbookcentre.ac.ke</t>
+          <t>accounts@textbookcentre.ke</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Kisumu</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kisumu City</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J77" s="1" t="n">
@@ -4965,7 +4965,7 @@
         <v>46022</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>1</v>
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Dorcas Otieno</t>
+          <t>Daniel Muthoni</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+254713380028</t>
+          <t>+254745607868</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>support@pedigreekenya.co.ke</t>
+          <t>orders@pedigreekenya.ke</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J78" s="1" t="n">
@@ -5024,7 +5024,7 @@
         <v>46022</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M78" t="b">
         <v>1</v>
@@ -5048,28 +5048,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kevin Kamau</t>
+          <t>Faith Kimani</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>+254746114338</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>+254702433632</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>admin@whiskaskenya.ke</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J79" s="1" t="n">
@@ -5079,7 +5083,7 @@
         <v>46022</v>
       </c>
       <c r="L79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>1</v>
@@ -5103,22 +5107,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mercy Kiprotich</t>
+          <t>John Njoroge</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>+254790386706</t>
+          <t>+254742718849</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>accounts@purinakenya.ke</t>
+          <t>orders@purinakenya.co.ke</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nakuru County</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5128,7 +5132,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J80" s="1" t="n">
@@ -5162,27 +5166,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Peter Mutua</t>
+          <t>Daniel Kimani</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>+254794928381</t>
+          <t>+254761261859</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>accounts@smartheartkenya.ke</t>
+          <t>info@smartheartkenya.ke</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kisumu</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kisumu City</t>
+          <t>Kilimani</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5197,7 +5201,7 @@
         <v>46022</v>
       </c>
       <c r="L81" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
@@ -5221,32 +5225,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Daniel Muthoni</t>
+          <t>Dennis Kariuki</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>+254745607868</t>
+          <t>+254720757246</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>orders@freshharvestsuppliers.ke</t>
+          <t>admin@freshharvestsuppliers.ke</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Machakos</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Athi River</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J82" s="1" t="n">
@@ -5256,7 +5260,7 @@
         <v>46022</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82" t="b">
         <v>1</v>
@@ -5280,32 +5284,32 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Faith Kimani</t>
+          <t>Peter Kimani</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>+254702433632</t>
+          <t>+254706897305</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>admin@greenfarmkenya.ke</t>
+          <t>admin@greenfarmkenya.ac.ke</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J83" s="1" t="n">
@@ -5315,7 +5319,7 @@
         <v>46022</v>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -5339,32 +5343,32 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>John Njoroge</t>
+          <t>Joyce Otieno</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>+254742718849</t>
+          <t>+254718475876</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>orders@naturefreshltd.co.ke</t>
+          <t>orders@naturefreshltd.ke</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Naivasha</t>
+          <t>Nairobi CBD</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J84" s="1" t="n">
@@ -5374,7 +5378,7 @@
         <v>46022</v>
       </c>
       <c r="L84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
@@ -5398,32 +5402,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Daniel Kimani</t>
+          <t>Kevin Odhiambo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>+254761261859</t>
+          <t>+254759501126</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>info@ farmchoicekenya.ke</t>
+          <t>support@farmchoicekenya.ac.ke</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kilimani</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J85" s="1" t="n">
@@ -5433,7 +5437,7 @@
         <v>46022</v>
       </c>
       <c r="L85" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
@@ -5457,32 +5461,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Dennis Kariuki</t>
+          <t>Grace Mwangi</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>+254720757246</t>
+          <t>+254796587853</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>admin@organicselectkenya.ke</t>
+          <t>orders@organicselectkenya.ac.ke</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Meru</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Athi River</t>
+          <t>Maua</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J86" s="1" t="n">
@@ -5492,7 +5496,7 @@
         <v>46022</v>
       </c>
       <c r="L86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M86" t="b">
         <v>1</v>
@@ -5506,42 +5510,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dormans Coffee - Nakuru Branch</t>
+          <t>Text Book Centre - Eldoret Branch</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tea &amp; Coffee</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>David Wanjiku</t>
+          <t>Dorcas Kamau</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>+254728274446</t>
+          <t>+254712503380</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>admin@dormanscoffee.ke</t>
+          <t>accounts@textbookcentre.co.ke</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Athi River</t>
+          <t>Nyali</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J87" s="1" t="n">
@@ -5551,7 +5555,7 @@
         <v>46022</v>
       </c>
       <c r="L87" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
@@ -5565,42 +5569,42 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Big Cold Ltd - Meru Branch</t>
+          <t>Java House Coffee - Nairobi Branch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frozen Foods</t>
+          <t>Tea &amp; Coffee</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Faith Kiprotich</t>
+          <t>James Ouma</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>+254726693418</t>
+          <t>+254768916118</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>admin@bigcoldltd.co.ke</t>
+          <t>admin@javahousecoffee.co.ke</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mombasa CBD</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J88" s="1" t="n">
@@ -5610,7 +5614,7 @@
         <v>46022</v>
       </c>
       <c r="L88" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M88" t="b">
         <v>1</v>
@@ -5624,7 +5628,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SmartHeart Kenya - Kakamega Branch</t>
+          <t>Whiskas Kenya - Meru Branch</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5634,17 +5638,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Victor Njoroge</t>
+          <t>Paul Mutua</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>254714583550</t>
+          <t>+254768892280</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>admin@smartheartkenya.ke</t>
+          <t>admin@whiskaskenya.ac.ke</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J89" s="1" t="n">
@@ -5669,7 +5673,7 @@
         <v>46022</v>
       </c>
       <c r="L89" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
@@ -5683,42 +5687,42 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dormans Coffee - Kakamega Branch</t>
+          <t>Broadways Bakery - Thika Branch</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tea &amp; Coffee</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Peter Muthoni</t>
+          <t>Daniel Odhiambo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>+254722716113</t>
+          <t>+254718442589</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>orders@dormanscoffee.ac.ke</t>
+          <t>admin@broadwaysbakery.ke</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J90" s="1" t="n">
@@ -5728,7 +5732,7 @@
         <v>46022</v>
       </c>
       <c r="L90" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
@@ -5742,42 +5746,42 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Perfetti Van Melle - Thika Branch</t>
+          <t>Tropical Heat Ltd - Kitale Branch</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Confectionery</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Esther Ouma</t>
+          <t>Grace Kiptoo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>+254722702733</t>
+          <t>+254716964749</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>orders@perfettivanmelle.ac.ke</t>
+          <t>accounts@tropicalheatltd.ke</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kajiado</t>
+          <t>Nyandarua</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kitengela</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J91" s="1" t="n">
@@ -5787,10 +5791,10 @@
         <v>46022</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5801,42 +5805,42 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Delamere Dairy - Machakos Branch</t>
+          <t>Kasuku Foods - Nakuru Branch</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Faith Nyambura</t>
+          <t>Peter Kariuki</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>+254796469435</t>
+          <t>+254700377304</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>sales@delameredairy.ac.ke</t>
+          <t>support@kasukufoods.co.ke</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J92" s="1" t="n">
@@ -5846,7 +5850,7 @@
         <v>46022</v>
       </c>
       <c r="L92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M92" t="b">
         <v>1</v>
@@ -5860,7 +5864,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fresh Harvest Suppliers - Kakamega Branch</t>
+          <t>Green Farm Kenya - Meru Branch</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5870,32 +5874,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Dorcas Otieno</t>
+          <t>Lucy Mwangi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>+254757482584</t>
+          <t>+254759688678</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>admin@freshharvestsuppliers.co.ke</t>
+          <t>orders@greenfarmkenya.ac.ke</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kiambu Town</t>
+          <t>Kitengela</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J93" s="1" t="n">
@@ -5919,42 +5923,42 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Varun Beverages Kenya - Kisumu Branch</t>
+          <t>Reckitt Benckiser - Mombasa Branch</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Samuel Kiprotich</t>
+          <t>John Kamau</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+254717970813</t>
+          <t>+254741221761</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>sales@varunbeverageskenya.ke</t>
+          <t>info@reckittbenckiser.co.ke</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Nakuru Town</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J94" s="1" t="n">
@@ -5964,7 +5968,7 @@
         <v>46022</v>
       </c>
       <c r="L94" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M94" t="b">
         <v>1</v>
@@ -5978,42 +5982,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Raha Premium - Thika Branch</t>
+          <t>Philips Kenya - Nyeri Branch</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Faith Kariuki</t>
+          <t>Ann Wanjiku</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>+254799943671</t>
+          <t>+254798613117</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>support@rahapremium.ke</t>
+          <t>support@philipskenya.ke</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Machakos Town</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J95" s="1" t="n">
@@ -6023,7 +6027,7 @@
         <v>46022</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
@@ -6037,37 +6041,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nivea Kenya - Meru Branch</t>
+          <t>Keringet Mineral Water - Meru Branch</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Esther Maina</t>
+          <t>Dennis Maina</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+254706807617</t>
+          <t>+254703517479</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>sales@niveakenya.ke</t>
+          <t>orders@keringetmineralwater.co.ke</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Meru</t>
+          <t>Kajiado</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Makutano</t>
+          <t>Ngong</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6096,37 +6100,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Unilever Kenya - Kisii Branch</t>
+          <t>Green Farm Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>David Njoroge</t>
+          <t>Joyce Achieng</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+254702139019</t>
+          <t>+254708925206</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>orders@unileverkenya.ke</t>
+          <t>support@greenfarmkenya.co.ke</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Nairobi CBD</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6141,7 +6145,7 @@
         <v>46022</v>
       </c>
       <c r="L97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M97" t="b">
         <v>1</v>
@@ -6155,42 +6159,42 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nivea Kenya - Meru Branch</t>
+          <t>Kasuku Foods - Machakos Branch</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Victor Njoroge</t>
+          <t>Daniel Njoroge</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>+254726786735</t>
+          <t>+254745362829</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>info@niveakenya.ke</t>
+          <t>sales@kasukufoods.co.ke</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J98" s="1" t="n">
@@ -6214,42 +6218,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Monster Energy Kenya - Thika Branch</t>
+          <t>Keringet Mineral Water - Machakos Branch</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mary Wanjiku</t>
+          <t>Kevin Mutua</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>+254768485178</t>
+          <t>+254703232915</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>support@monsterenergykenya.ac.ke</t>
+          <t>admin@keringetmineralwater.ke</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J99" s="1" t="n">
@@ -6259,7 +6263,7 @@
         <v>46022</v>
       </c>
       <c r="L99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M99" t="b">
         <v>1</v>
@@ -6273,42 +6277,42 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bidco Africa - Thika Branch</t>
+          <t>Tropical Heat Ltd - Kitale Branch</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Brian Nyambura</t>
+          <t>Dorcas Kiprotich</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>+254701153035</t>
+          <t>+254714744986</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>orders@bidcoafrica.co.ke</t>
+          <t>info@tropicalheatltd.ac.ke</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Machakos</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Mlolongo</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J100" s="1" t="n">
@@ -6318,10 +6322,10 @@
         <v>46022</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -6332,42 +6336,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Text Book Centre - Nakuru Branch</t>
+          <t>Lato Milk - Thika Branch</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Daniel Nyambura</t>
+          <t>David Wambui</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>+254700390743</t>
+          <t>+254790565108</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>sales@textbookcentre.co.ke</t>
+          <t>info@latomilk.co.ke</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J101" s="1" t="n">
@@ -6377,7 +6381,7 @@
         <v>46022</v>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M101" t="b">
         <v>1</v>
@@ -6391,42 +6395,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kinangop Dairy - Kisumu Branch </t>
+          <t>Green Farm Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Faith Ouma</t>
+          <t>Esther Nyambura</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>+254720116547</t>
+          <t>+254743409222</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>sales@kinangopdairy.ke</t>
+          <t>accounts@greenfarmkenya.ac.ke</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 60</t>
         </is>
       </c>
       <c r="J102" s="1" t="n">
@@ -6436,7 +6440,7 @@
         <v>46022</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M102" t="b">
         <v>1</v>
@@ -6450,42 +6454,42 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Upfield Kenya - Thika Branch</t>
+          <t>Farm Choice Kenya - Kakamega Branch</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Samuel Ouma</t>
+          <t>Ann Muthoni</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+254706573962</t>
+          <t>+254714533914</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>support@upfieldkenya,co.ke</t>
+          <t>orders@farmchoicekenya.ke</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J103" s="1" t="n">
@@ -6495,7 +6499,7 @@
         <v>46022</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -6509,42 +6513,42 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kinangop Dairy - Nairobi Branch</t>
+          <t>Highlands Drinks Ltd - Meru Branch</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ann Wanjiku</t>
+          <t>Lucy Odhiambo</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>+254741847006</t>
+          <t>+254705972176</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>accounts@kinangopdairy.co.ke</t>
+          <t>info@highlandsdrinksltd.co.ke</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Kwale</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J104" s="1" t="n">
@@ -6554,7 +6558,7 @@
         <v>46022</v>
       </c>
       <c r="L104" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M104" t="b">
         <v>1</v>
@@ -6568,42 +6572,42 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SmartHeart Kenya - Kakamega Branch</t>
+          <t>Lato Milk - Machakos Branch</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pet Care</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Esther Nyambura</t>
+          <t>David Kimani</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>+254743409222</t>
+          <t>+254722797660</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>accounts@smartheartkenya.ac.ke</t>
+          <t>accounts@latomilk.ac.ke</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Laikipia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Nanyuki</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Net 60</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J105" s="1" t="n">
@@ -6613,7 +6617,7 @@
         <v>46022</v>
       </c>
       <c r="L105" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
@@ -6627,42 +6631,42 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Farm Choice Kenya - Kakamega Branch</t>
+          <t>Luminarc Kenya - Nakuru Branch</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fresh Produce</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ann Muthoni</t>
+          <t>Lucy Achieng</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>+254714533914</t>
+          <t>+254799213475</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>orders@farmchoicekenya.ke</t>
+          <t>orders@luminarckenya.ac.ke</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Nakuru</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Gilgil</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J106" s="1" t="n">
@@ -6672,7 +6676,7 @@
         <v>46022</v>
       </c>
       <c r="L106" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M106" t="b">
         <v>1</v>
@@ -6686,42 +6690,42 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Highlands Drinks Ltd - Meru Branch</t>
+          <t>Colgate Palmolive - Kitale Branch</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lucy Odhiambo</t>
+          <t>Paul Mutua</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>+254705972176</t>
+          <t>+254701289179</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>info@highlandsdrinksltd.co.ke</t>
+          <t>orders@colgatepalmolive.ac.ke</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J107" s="1" t="n">
@@ -6731,7 +6735,7 @@
         <v>46022</v>
       </c>
       <c r="L107" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M107" t="b">
         <v>1</v>
@@ -6745,42 +6749,42 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lato Milk - Machakos Branch</t>
+          <t>Kasuku Foods - Machakos Branch</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>David Kimani</t>
+          <t>Daniel Mwangi</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>+254722797660</t>
+          <t>+254705882354</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>accounts@latomilk.ac.ke</t>
+          <t>support@kasukufoods.co.ke</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Laikipia</t>
+          <t>Embu</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Nanyuki</t>
+          <t>Embu Town</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Net 7</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J108" s="1" t="n">
@@ -6804,42 +6808,42 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luminarc Kenya - Nakuru Branch</t>
+          <t>Broadways Bakery - Kisii Branch</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Lucy Achieng</t>
+          <t>John Njoroge</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>+254799213475</t>
+          <t>+254710891083</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>orders@luminarckenya.ac.ke</t>
+          <t>support@broadwaysbakery.co.ke</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nakuru</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Gilgil</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J109" s="1" t="n">
@@ -6849,7 +6853,7 @@
         <v>46022</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M109" t="b">
         <v>1</v>
@@ -6863,42 +6867,42 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Colgate Palmolive - Kitale Branch</t>
+          <t>Tefal Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paul Mutua</t>
+          <t>Grace Chebet</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>+254701289179</t>
+          <t>+254793637234</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>orders@colgatepalmolive.ac.ke</t>
+          <t>info@tefalkenya.ke</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J110" s="1" t="n">
@@ -6908,7 +6912,7 @@
         <v>46022</v>
       </c>
       <c r="L110" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M110" t="b">
         <v>1</v>
@@ -6922,42 +6926,42 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kasuku Foods - Machakos Branch</t>
+          <t>Tefal Kenya - Kitale Branch</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Daniel Mwangi</t>
+          <t>Faith Kariuki</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>+254705882354</t>
+          <t>+254758157443</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>support@kasukufoods.co.ke</t>
+          <t>info@tefalkenya.co.ke</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Embu</t>
+          <t>Nyeri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Embu Town</t>
+          <t>Nyeri Town</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 30</t>
         </is>
       </c>
       <c r="J111" s="1" t="n">
@@ -6967,7 +6971,7 @@
         <v>46022</v>
       </c>
       <c r="L111" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M111" t="b">
         <v>1</v>
@@ -6981,42 +6985,42 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Broadways Bakery - Kisii Branch</t>
+          <t>Kenchic Ltd - Mombasa Branch</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Meat &amp; Poultry</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>John Njoroge</t>
+          <t>Ann Kiptoo</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>+254710891083</t>
+          <t>+254708498676</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>support@broadwaysbakery.co.ke</t>
+          <t>support@kenchicltd.ac.ke</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kasarani</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J112" s="1" t="n">
@@ -7026,7 +7030,7 @@
         <v>46022</v>
       </c>
       <c r="L112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M112" t="b">
         <v>1</v>
@@ -7040,42 +7044,42 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tefal Kenya - Machakos Branch</t>
+          <t>Happy Cow Ltd - Nyeri Branch</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Grace Chebet</t>
+          <t>Peter Omondi</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>+254793637234</t>
+          <t>+254748550137</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>info@tefalkenya.ke</t>
+          <t>support@happycowltd.ke</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Kilifi</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kilifi Town</t>
+          <t>Kasarani</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Cash on Delivery</t>
         </is>
       </c>
       <c r="J113" s="1" t="n">
@@ -7085,7 +7089,7 @@
         <v>46022</v>
       </c>
       <c r="L113" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M113" t="b">
         <v>1</v>
@@ -7099,42 +7103,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tefal Kenya - Kitale Branch</t>
+          <t>Kenchic Ltd - Kisumu Branch</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Meat &amp; Poultry</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Faith Kariuki</t>
+          <t>Mary Odhiambo</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>+254758157443</t>
+          <t>+254727985506</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>info@tefalkenya.co.ke</t>
+          <t>info@kenchicltd.co.ke</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nyeri</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Nyeri Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Net 30</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J114" s="1" t="n">
@@ -7144,7 +7148,7 @@
         <v>46022</v>
       </c>
       <c r="L114" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M114" t="b">
         <v>1</v>
@@ -7158,37 +7162,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kenchic Ltd - Mombasa Branch</t>
+          <t>Victory Farms - Nakuru Branch</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Meat &amp; Poultry</t>
+          <t>Fish &amp; Seafood</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ann Kiptoo</t>
+          <t>Peter Kiprotich</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>+254708498676</t>
+          <t>+254760219565</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>support@kenchicltd.ac.ke</t>
+          <t>support@victoryfarms.ac.ke</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Murang'a</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kasarani</t>
+          <t>Murang'a Town</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7203,10 +7207,10 @@
         <v>46022</v>
       </c>
       <c r="L115" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7217,42 +7221,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Happy Cow Ltd - Nyeri Branch</t>
+          <t>Nature Fresh Ltd - Kisumu Branch</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Fresh Produce</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Peter Omondi</t>
+          <t>Daniel Mutua</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>+254748550137</t>
+          <t>+254712281926</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>support@happycowltd.ke</t>
+          <t>support@naturefreshltd.co.ke</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Kakamega</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kasarani</t>
+          <t>Kakamega Town</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cash on Delivery</t>
+          <t>Advance Payment</t>
         </is>
       </c>
       <c r="J116" s="1" t="n">
@@ -7262,7 +7266,7 @@
         <v>46022</v>
       </c>
       <c r="L116" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M116" t="b">
         <v>1</v>
@@ -7276,37 +7280,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kenchic Ltd - Kisumu Branch</t>
+          <t>Unilever Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Meat &amp; Poultry</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mary Odhiambo</t>
+          <t>Victor Nyambura</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>+254727985506</t>
+          <t>+254720757685</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>info@kenchicltd.co.ke</t>
+          <t>orders@unileverkenya.co.ke</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Trans Nzoia</t>
+          <t>Bungoma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kitale</t>
+          <t>Bungoma Town</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7321,7 +7325,7 @@
         <v>46022</v>
       </c>
       <c r="L117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M117" t="b">
         <v>1</v>
@@ -7335,42 +7339,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Victory Farms - Nakuru Branch</t>
+          <t>Nestlé Kenya - Machakos Branch</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fish &amp; Seafood</t>
+          <t>Tea &amp; Coffee</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Peter Kiprotich</t>
+          <t>Samuel Odhiambo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>+254760219565</t>
+          <t>+254719584172</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>support@victoryfarms.ac.ke</t>
+          <t>accounts@nestlékenya.co.ke</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Murang'a</t>
+          <t>Kiambu</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Murang'a Town</t>
+          <t>Kiambu Town</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Net 15</t>
+          <t>Net 7</t>
         </is>
       </c>
       <c r="J118" s="1" t="n">
@@ -7380,10 +7384,10 @@
         <v>46022</v>
       </c>
       <c r="L118" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -7394,42 +7398,42 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nature Fresh Ltd - Kisumu Branch</t>
+          <t>Pembe Flour Mills - Machakos Branch</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fresh Produce</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Daniel Mutua</t>
+          <t>Dorcas Ouma</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>+254712281926</t>
+          <t>+254746930281</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>support@naturefreshltd.co.ke</t>
+          <t>admin@pembeflourmills.co.ke</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Kakamega</t>
+          <t>Trans Nzoia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kakamega Town</t>
+          <t>Kitale</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Advance Payment</t>
+          <t>Net 45</t>
         </is>
       </c>
       <c r="J119" s="1" t="n">
@@ -7439,7 +7443,7 @@
         <v>46022</v>
       </c>
       <c r="L119" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M119" t="b">
         <v>1</v>
@@ -7453,42 +7457,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Unilever Kenya - Machakos Branch</t>
+          <t>Exe Consumer Brands - Nairobi Branch</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Victor Nyambura</t>
+          <t>Joyce Odhiambo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+254720757685</t>
+          <t>+254742777513</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>orders@unileverkenya.co.ke</t>
+          <t>sales@execonsumerbrands.co.ke</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bungoma</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bungoma Town</t>
+          <t>Kilifi Town</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Net 45</t>
+          <t>Net 15</t>
         </is>
       </c>
       <c r="J120" s="1" t="n">
@@ -7498,7 +7502,7 @@
         <v>46022</v>
       </c>
       <c r="L120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M120" t="b">
         <v>1</v>
@@ -7512,37 +7516,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nestlé Kenya - Machakos Branch</t>
+          <t>Crown Foods - Meru Branch</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tea &amp; Coffee</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Samuel Odhiambo</t>
+          <t>Esther Kimani</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>+254719584172</t>
+          <t>+254794454803</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>accounts@nestlékenya.co.ke</t>
+          <t>admin@crownfoods.ac.ke</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Kiambu</t>
+          <t>Kirinyaga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kiambu Town</t>
+          <t>Kerugoya</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7557,30 +7561,11 @@
         <v>46022</v>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M121" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>+254793637234</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
